--- a/leads_psicologo_sao_paulo.xlsx
+++ b/leads_psicologo_sao_paulo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N29"/>
+  <dimension ref="A1:N49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,10 +526,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(SA) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(11) 96862-0525</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5511968620525</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/LCS%20Psicologia%20sao%20paulo</t>
@@ -553,12 +557,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20LCS%20Psicologia%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5511968620525?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20LCS%20Psicologia%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20LCS%20Psicologia%3F</t>
+          <t>https://wa.me/5511968620525?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20LCS%20Psicologia%3F</t>
         </is>
       </c>
     </row>
@@ -861,12 +865,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Consultrio de psiclogo em So Paulo</t>
+          <t>Psiclogo, Conselheiro, Terapeuta perto de mim</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Consultório de psicólogo em São Paulo - Mental One</t>
+          <t>Psicólogo, Conselheiro, Terapeuta perto de mim em São Paulo ...</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -881,7 +885,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Consultório de psicólogo na Zona Sul. Especialista em terapia cognitivo comportamental....</t>
+          <t>Psicólogo clínico, com atuação no atendimento de crianças, adolescentes e adultos. Trabalho com acol...</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -891,28 +895,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.mentalone.com.br/consultorio-psicologo-sao-paulo</t>
+          <t>https://mentalzon.com/pt/city/Brasil/São+Paulo/São+Paulo</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(11) 91454-0891</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5511914540891</t>
-        </is>
-      </c>
+          <t>(SA) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Consultrio%20de%20psiclogo%20em%20So%20Paulo%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Psiclogo%2C%20Conselheiro%2C%20Terapeuta%20perto%20de%20mim%20sao%20paulo</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Consultrio de psiclogo em So Paulo aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Psiclogo, Conselheiro, Terapeuta perto de mim aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -922,29 +922,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Consultrio de psiclogo em So Paulo?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Psiclogo, Conselheiro, Terapeuta perto de mim?</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://wa.me/5511914540891?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Consultrio%20de%20psiclogo%20em%20So%20Paulo%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psiclogo%2C%20Conselheiro%2C%20Terapeuta%20perto%20de%20mim%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://wa.me/5511914540891?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Consultrio%20de%20psiclogo%20em%20So%20Paulo%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psiclogo%2C%20Conselheiro%2C%20Terapeuta%20perto%20de%20mim%3F</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Gustavo Cicilini</t>
+          <t>Consultrio de psiclogo em So Paulo</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Gustavo Cicilini - Psicólogo e Consultor de Pessoas | LinkedIn</t>
+          <t>Consultório de psicólogo em São Paulo - Mental One</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Psicólogo e executivo com mais de 25 anos de experiência em Recursos Humanos em… · Experiência: Psic...</t>
+          <t>Consultório de psicólogo na Zona Sul. Especialista em terapia cognitivo comportamental....</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -969,24 +969,28 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://br.linkedin.com/in/gustavocicilini</t>
+          <t>https://www.mentalone.com.br/consultorio-psicologo-sao-paulo</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(SA) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(11) 97092-5229</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5511970925229</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Gustavo%20Cicilini%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Consultrio%20de%20psiclogo%20em%20So%20Paulo%20sao%20paulo</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Gustavo Cicilini aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Consultrio de psiclogo em So Paulo aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -996,17 +1000,17 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Gustavo Cicilini?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Consultrio de psiclogo em So Paulo?</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Gustavo%20Cicilini%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5511970925229?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Consultrio%20de%20psiclogo%20em%20So%20Paulo%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Gustavo%20Cicilini%3F</t>
+          <t>https://wa.me/5511970925229?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Consultrio%20de%20psiclogo%20em%20So%20Paulo%3F</t>
         </is>
       </c>
     </row>
@@ -1048,10 +1052,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(SA) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(11) 5102-3493</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>551151023493</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/Psicloga%20Brooklin%20sao%20paulo</t>
@@ -1075,12 +1083,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psicloga%20Brooklin%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/551151023493?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psicloga%20Brooklin%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psicloga%20Brooklin%3F</t>
+          <t>https://wa.me/551151023493?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psicloga%20Brooklin%3F</t>
         </is>
       </c>
     </row>
@@ -1196,14 +1204,10 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(11) 4502-4752</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>551145024752</t>
-        </is>
-      </c>
+          <t>(SA) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/Portal%20sao%20paulo</t>
@@ -1227,24 +1231,24 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://wa.me/551145024752?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Portal%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Portal%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://wa.me/551145024752?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Portal%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Portal%3F</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Psicologo Transpessoal Em Perdizes</t>
+          <t>Psiclogo, So Paulo, SP</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Psicologo Transpessoal Em Perdizes</t>
+          <t>Psicólogo, São Paulo, SP - Central Terapia</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1259,7 +1263,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Psicologo Transpessoal em Perdizes Psicoterapia, autoconhecimento, prevenção e tratamento de distúrb...</t>
+          <t>Psicólogos perto de você! Obtenha suporte e consulta especializada com os psicólogos (as) mais recom...</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1269,28 +1273,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.cuiket.com.br/empresa/psicologo-transpessoal-em-perdizes_5001176.html</t>
+          <t>https://centralterapia.com.br/psicologo/sao-paulo/</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(11) 2368-1764</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>551123681764</t>
-        </is>
-      </c>
+          <t>(SA) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Psicologo%20Transpessoal%20Em%20Perdizes%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Psiclogo%2C%20So%20Paulo%2C%20SP%20sao%20paulo</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Psicologo Transpessoal Em Perdizes aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Psiclogo, So Paulo, SP aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1300,29 +1300,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Psicologo Transpessoal Em Perdizes?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Psiclogo, So Paulo, SP?</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://wa.me/551123681764?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psicologo%20Transpessoal%20Em%20Perdizes%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psiclogo%2C%20So%20Paulo%2C%20SP%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://wa.me/551123681764?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psicologo%20Transpessoal%20Em%20Perdizes%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psiclogo%2C%20So%20Paulo%2C%20SP%3F</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>VLOG vivendo em Sao Paulo: brunch, brech &amp; bo</t>
+          <t>Terapia e Psicloga Online por</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>VLOG vivendo em Sao Paulo: brunch, brechó &amp; boteco - YouTube</t>
+          <t>Terapia e Psicóloga Online por whatsapp ☆</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1337,17 +1337,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>О сервисе Прессе Авторские права Связаться с нами Авторам Рекламодателям......</t>
+          <t>A terapia online pode ser realizada via WhatsApp ou plataformas específicas de videoconferência, gar...</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SEM SITE PRÓPRIO (OPORTUNIDADE 🔥)</t>
+          <t>SITE ATIVO 📱</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sem Site Cadastrado</t>
+          <t>https://www.psicologiasemfronteiras.com.br/p/psicologa-online-via-skype-ou-whatsapp.html</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1358,13 +1358,13 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/VLOG%20vivendo%20em%20Sao%20Paulo%3A%20brunch%2C%20brech%20%26%20bo%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Terapia%20e%20Psicloga%20Online%20por%20sao%20paulo</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da VLOG vivendo em Sao Paulo: brunch, brech &amp; bo aí em Sao paulo no Google e vi que vocês ainda não têm um site próprio para celular.
+Vi o perfil da Terapia e Psicloga Online por aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1374,29 +1374,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a VLOG vivendo em Sao Paulo: brunch, brech &amp; bo?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Terapia e Psicloga Online por?</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20VLOG%20vivendo%20em%20Sao%20Paulo%3A%20brunch%2C%20brech%20%26%20bo%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Terapia%20e%20Psicloga%20Online%20por%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20VLOG%20vivendo%20em%20Sao%20Paulo%3A%20brunch%2C%20brech%20%26%20bo%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Terapia%20e%20Psicloga%20Online%20por%3F</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Consultrio Psiclogos Berrini</t>
+          <t>PSICLOGA ONLINE: Terapia por Videochamada /</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Consultório Psicólogos Berrini - Mental Health Clinic in Itaim Bi</t>
+          <t>PSICÓLOGA ONLINE: Terapia por Videochamada / Whatsapp ...</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>consultório psicólogos berrini itaim bibi são paulo.Consultório Psicólogos Berrini. Rua Alcides Rica...</t>
+          <t>Pode ser que isso pareça muito artificial e nos faça ficar com um pé atrás. No entanto, um psicólogo...</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1421,24 +1421,28 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://foursquare.com/v/consultório-psicólogos-berrini/562623d9498e934035665ab1</t>
+          <t>https://www.rachelmontenegro.psc.br/psicologa-online</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(SA) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(71) 99264-3441</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5571992643441</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Consultrio%20Psiclogos%20Berrini%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/PSICLOGA%20ONLINE%3A%20Terapia%20por%20Videochamada%20/%20sao%20paulo</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Consultrio Psiclogos Berrini aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da PSICLOGA ONLINE: Terapia por Videochamada / aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1448,29 +1452,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Consultrio Psiclogos Berrini?</t>
+Posso te mandar a prévia demonstrativa que fiz para a PSICLOGA ONLINE: Terapia por Videochamada /?</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Consultrio%20Psiclogos%20Berrini%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5571992643441?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20PSICLOGA%20ONLINE%3A%20Terapia%20por%20Videochamada%20/%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Consultrio%20Psiclogos%20Berrini%3F</t>
+          <t>https://wa.me/5571992643441?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20PSICLOGA%20ONLINE%3A%20Terapia%20por%20Videochamada%20/%3F</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Psiclogo Terapeuta Santana</t>
+          <t>Psiclogo Terapeuta Preo Anlia Franco</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Psicólogo Terapeuta Santana - Psico Plus</t>
+          <t>Psicólogo Terapeuta Preço Anália Franco - Psico Plus</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1485,7 +1489,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Faça seu orçamento por Whatsapp. Rua Gomes de Carvalho 768, 2º andar - São Paulo - SP.onde encontrar...</t>
+          <t>Clínicas de psicologia em São Paulo: Encontre o apoio que você precisa para sua saúde mental.onde en...</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1495,24 +1499,28 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.clinicapsicoplus.com.br/terapia/terapia-em-sao-paulo/psicologo-terapeuta-santana</t>
+          <t>https://www.clinicapsicoplus.com.br/terapia/terapia-em-sao-paulo/psicologo-terapeuta-preco-analia-franco</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(SA) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(14) 3841-2400</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>551438412400</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Psiclogo%20Terapeuta%20Santana%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Psiclogo%20Terapeuta%20Preo%20Anlia%20Franco%20sao%20paulo</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Psiclogo Terapeuta Santana aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Psiclogo Terapeuta Preo Anlia Franco aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1522,29 +1530,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Psiclogo Terapeuta Santana?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Psiclogo Terapeuta Preo Anlia Franco?</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psiclogo%20Terapeuta%20Santana%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/551438412400?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psiclogo%20Terapeuta%20Preo%20Anlia%20Franco%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psiclogo%20Terapeuta%20Santana%3F</t>
+          <t>https://wa.me/551438412400?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psiclogo%20Terapeuta%20Preo%20Anlia%20Franco%3F</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ajuda emocional: quando aconselhvel procurar</t>
+          <t>36 avaliaes sobre Psicloga Alessa Brando Latb</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ajuda emocional: quando é aconselhável procurar</t>
+          <t>36 avaliações sobre Psicóloga Alessa Brandão Latíbulo Consultório</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1559,7 +1567,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atendimento individual para questões de relacionamento. Terapia de família e casacologa sp, Psicólog...</t>
+          <t>Avaliações » Psicologo » São Paulo » Sao paulo » Psicologa alessa brandao latib.(Psicólogo) em São P...</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1569,24 +1577,28 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.psicologapaulista.com.br/2026/02/ajuda-emocional-quando-e-aconselhavel.html</t>
+          <t>https://avaliacoesbrasil.com/psicologo/sao-paulo/psicologa-alessa-brandao-latib/</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(SA) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(19) 99997-0207</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5519999970207</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Ajuda%20emocional%3A%20quando%20aconselhvel%20procurar%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/36%20avaliaes%20sobre%20Psicloga%20Alessa%20Brando%20Latb%20sao%20paulo</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Ajuda emocional: quando aconselhvel procurar aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da 36 avaliaes sobre Psicloga Alessa Brando Latb aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1596,29 +1608,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Ajuda emocional: quando aconselhvel procurar?</t>
+Posso te mandar a prévia demonstrativa que fiz para a 36 avaliaes sobre Psicloga Alessa Brando Latb?</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Ajuda%20emocional%3A%20quando%20aconselhvel%20procurar%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5519999970207?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%2036%20avaliaes%20sobre%20Psicloga%20Alessa%20Brando%20Latb%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Ajuda%20emocional%3A%20quando%20aconselhvel%20procurar%3F</t>
+          <t>https://wa.me/5519999970207?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%2036%20avaliaes%20sobre%20Psicloga%20Alessa%20Brando%20Latb%3F</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Yahoo Search</t>
+          <t>Ajuda emocional: quando aconselhvel procurar</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Yahoo Search – Busca na Web</t>
+          <t>Ajuda emocional: quando é aconselhável procurar</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1633,7 +1645,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>O mecanismo de busca que ajuda a localizar exatamente o que você procura. Busque as informações, víd...</t>
+          <t>Atendimento individual para questões de relacionamento. Terapia de família e casacologa sp, Psicólog...</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1643,7 +1655,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://br.search.yahoo.com/?fr2=p:fprd,mkt:br</t>
+          <t>https://www.psicologapaulista.com.br/2026/02/ajuda-emocional-quando-e-aconselhavel.html</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1654,13 +1666,13 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Yahoo%20Search%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Ajuda%20emocional%3A%20quando%20aconselhvel%20procurar%20sao%20paulo</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Yahoo Search aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Ajuda emocional: quando aconselhvel procurar aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1670,29 +1682,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Yahoo Search?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Ajuda emocional: quando aconselhvel procurar?</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Yahoo%20Search%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Ajuda%20emocional%3A%20quando%20aconselhvel%20procurar%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Yahoo%20Search%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Ajuda%20emocional%3A%20quando%20aconselhvel%20procurar%3F</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Detran</t>
+          <t>Psicologa Online: Acolhimento Humanizado</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Detran</t>
+          <t>Psicologa Online: Acolhimento Humanizado</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1707,38 +1719,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Você não fez login, ou sua sessão expirou. Redirecionando para a página de login....</t>
+          <t>Psicologa online por whatsapp, ou presencial na Bela vista. Agende sua sessão com acolhimento humani...</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SITE ATIVO 📱</t>
+          <t>SITE FORA DO AR (ERRO 404) 🚨</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.detran.sp.gov.br/session_timeout.do</t>
+          <t>https://www.psicologaresponde.com.br/2014/12/psicologo-sp-online_28.html</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(15) 5193-6100</t>
+          <t>(11) 2661-5000</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>551551936100</t>
+          <t>551126615000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Detran%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Psicologa%20Online%3A%20Acolhimento%20Humanizado%20sao%20paulo</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Detran aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Psicologa Online: Acolhimento Humanizado aí em Sao paulo no Google e fui tentar acessar o site de vocês e vi que está fora do ar.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1748,29 +1760,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Detran?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Psicologa Online: Acolhimento Humanizado?</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>https://wa.me/551551936100?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Detran%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/551126615000?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psicologa%20Online%3A%20Acolhimento%20Humanizado%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20fui%20tentar%20acessar%20o%20site%20de%20voc%C3%AAs%20e%20vi%20que%20est%C3%A1%20fora%20do%20ar.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://wa.me/551551936100?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Detran%3F</t>
+          <t>https://wa.me/551126615000?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psicologa%20Online%3A%20Acolhimento%20Humanizado%3F</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>OKESTREAM</t>
+          <t>Yahoo Search</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>OKESTREAM - Nonton Bola Online Gratis Tanpa Buffering</t>
+          <t>Yahoo Search – Busca na Web</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1785,7 +1797,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Okestream menyediakan live streaming sepakbola terlengkap dan terbaik se Indonesia. Nonton bola sema...</t>
+          <t>ex-diretor de futebol do São Paulo....</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1795,28 +1807,28 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://okestream.yachts/</t>
+          <t>https://br.search.yahoo.com/?fr2=p:fprd,mkt:br</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(62) 0215-5503</t>
+          <t>(02) 96777-3000</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>556202155503</t>
+          <t>5502967773000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/OKESTREAM%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Yahoo%20Search%20sao%20paulo</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da OKESTREAM aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Yahoo Search aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1826,29 +1838,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a OKESTREAM?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Yahoo Search?</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>https://wa.me/556202155503?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20OKESTREAM%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5502967773000?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Yahoo%20Search%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://wa.me/556202155503?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20OKESTREAM%3F</t>
+          <t>https://wa.me/5502967773000?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Yahoo%20Search%3F</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Link to instagram.com</t>
+          <t>OKESTREAM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Link to instagram.com</t>
+          <t>OKESTREAM - Nonton Bola Online Gratis Tanpa Buffering</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1863,17 +1875,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>The site owner hides the web page description....</t>
+          <t>São Paulo....</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SEM SITE PRÓPRIO (OPORTUNIDADE 🔥)</t>
+          <t>SITE ATIVO 📱</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sem Site Cadastrado</t>
+          <t>https://okestream.yachts/</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1884,13 +1896,13 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Link%20to%20instagram.com%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/OKESTREAM%20sao%20paulo</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Link to instagram.com aí em Sao paulo no Google e vi que vocês ainda não têm um site próprio para celular.
+Vi o perfil da OKESTREAM aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1900,29 +1912,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Link to instagram.com?</t>
+Posso te mandar a prévia demonstrativa que fiz para a OKESTREAM?</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Link%20to%20instagram.com%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20OKESTREAM%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Link%20to%20instagram.com%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20OKESTREAM%3F</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Elaine ferreira psicloga clnica, psicologo...</t>
+          <t>Terappia</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Elaine ferreira psicóloga clínica, psicologo...</t>
+          <t>Terappia - Psicologia Online. Consultas a partir de R$ 40 ...</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1937,34 +1949,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bairro: Freguesia do Ó. Cidade: São Paulo. Estado: SP.Sua mensagem será enviada para nossa equipe e ...</t>
+          <t>Terapia online com psicólogos via WhatsApp. Consultas a partir de R$ 40. Encontre o seu psicólogo on...</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SITE ATIVO 📱</t>
+          <t>SEM SITE PRÓPRIO (OPORTUNIDADE 🔥)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.terapyas.com.br/sobre/elaine-ferreira-psicologa-clinica-psicologo-atendimento-psicologico-e-terapia-sao-paulo-sp</t>
+          <t>Sem Site Cadastrado</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(SA) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(21) 99985-0091</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5521999850091</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Elaine%20ferreira%20psicloga%20clnica%2C%20psicologo...%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Terappia%20sao%20paulo</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Elaine ferreira psicloga clnica, psicologo... aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Terappia aí em Sao paulo no Google e vi que vocês ainda não têm um site próprio para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1974,29 +1990,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Elaine ferreira psicloga clnica, psicologo...?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Terappia?</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Elaine%20ferreira%20psicloga%20clnica%2C%20psicologo...%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5521999850091?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Terappia%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Elaine%20ferreira%20psicloga%20clnica%2C%20psicologo...%3F</t>
+          <t>https://wa.me/5521999850091?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Terappia%3F</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Terapia online com psiclogos disponveis 24h p</t>
+          <t>Clnica de psicologia em So Paulo</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Terapia online com psicólogos disponíveis 24h por dia | Zenklub</t>
+          <t>Clínica de psicologia em São Paulo - PsicoClinic</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2011,7 +2027,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Estamos sempre com você. Todo dia e a qualquer hora, nossos especialistas estarão disponíveis para a...</t>
+          <t>Com psicóloga em São Paulo referência em tratamentos de excelência, a PsicoClinic é reconhecida pelo...</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2021,7 +2037,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://zenklub.com.br/</t>
+          <t>https://www.psicoclinic.com.br/</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2032,13 +2048,13 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Terapia%20online%20com%20psiclogos%20disponveis%2024h%20p%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Clnica%20de%20psicologia%20em%20So%20Paulo%20sao%20paulo</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Terapia online com psiclogos disponveis 24h p aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Clnica de psicologia em So Paulo aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2048,29 +2064,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Terapia online com psiclogos disponveis 24h p?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Clnica de psicologia em So Paulo?</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Terapia%20online%20com%20psiclogos%20disponveis%2024h%20p%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clnica%20de%20psicologia%20em%20So%20Paulo%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Terapia%20online%20com%20psiclogos%20disponveis%2024h%20p%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clnica%20de%20psicologia%20em%20So%20Paulo%3F</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ofertas e Cupons de</t>
+          <t>Elton Alexandre, Psiclogo Vila Mariana So Pau</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ofertas e Cupons de Desconto para Porto Alegre, Gramado e Mais!</t>
+          <t>Elton Alexandre, Psicólogo Vila Mariana São Paulo - Telefone...</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2085,7 +2101,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Central de atendimento. Icone WhatsApp....</t>
+          <t>Qual o telefone de Elton Alexandre, Psicólogo Vila Mariana São Paulo? O número de telefone é: +55 11...</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2095,24 +2111,28 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.tcheofertas.com.br/</t>
+          <t>https://www.benditoguia.com.br/empresa/elton-alexandre-psicologo-vila-mariana-sao-paulo</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(SA) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(11) 95289-2329</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5511952892329</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Ofertas%20e%20Cupons%20de%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Elton%20Alexandre%2C%20Psiclogo%20Vila%20Mariana%20So%20Pau%20sao%20paulo</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Ofertas e Cupons de aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Elton Alexandre, Psiclogo Vila Mariana So Pau aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2122,29 +2142,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Ofertas e Cupons de?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Elton Alexandre, Psiclogo Vila Mariana So Pau?</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Ofertas%20e%20Cupons%20de%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5511952892329?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Elton%20Alexandre%2C%20Psiclogo%20Vila%20Mariana%20So%20Pau%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Ofertas%20e%20Cupons%20de%3F</t>
+          <t>https://wa.me/5511952892329?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Elton%20Alexandre%2C%20Psiclogo%20Vila%20Mariana%20So%20Pau%3F</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Super Portal</t>
+          <t>Inddex PSICOLOGO GUSTAVO ROBERTO CNPJ...</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Super Portal</t>
+          <t>Inddex · PSICOLOGO GUSTAVO ROBERTO · CNPJ...</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2159,7 +2179,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Marcação consulta/exame Atendimento....</t>
+          <t>Inddex/SP/SAO Paulo/Psicologo Gustavo Roberto.Telefones, e-mail, capital social, sócios e CNAEs secu...</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2169,24 +2189,28 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://portal-beneficiario.hapvida.com.br/</t>
+          <t>https://inddex.com.br/empresa/49186818000130/atividades-de-psicologia-e-psicanalise-sao-paulo-sp</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(SA) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(49) 1868-1800</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>554918681800</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Super%20Portal%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Inddex%20PSICOLOGO%20GUSTAVO%20ROBERTO%20CNPJ...%20sao%20paulo</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Super Portal aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Inddex PSICOLOGO GUSTAVO ROBERTO CNPJ... aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2196,29 +2220,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Super Portal?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Inddex PSICOLOGO GUSTAVO ROBERTO CNPJ...?</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Super%20Portal%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/554918681800?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Inddex%20PSICOLOGO%20GUSTAVO%20ROBERTO%20CNPJ...%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Super%20Portal%3F</t>
+          <t>https://wa.me/554918681800?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Inddex%20PSICOLOGO%20GUSTAVO%20ROBERTO%20CNPJ...%3F</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>hering.com.br</t>
+          <t>Psicloga Aline Quirosa, So Paulo (2026)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>hering.com.br</t>
+          <t>Psicóloga Aline Quirosa, São Paulo (2026)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2233,7 +2257,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Nossos canais oficias são: @Hering_oficial e @Ciaheringoficial no Instagram......</t>
+          <t>Brasil. São Paulo, SP. Psicóloga Aline Quirosa.Endereço. Telefone. Horário de Funcionamento. Notific...</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2243,7 +2267,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.hering.com.br/</t>
+          <t>https://www.findhealthclinics.org/BR/São-Paulo/103266911851448/Psicóloga-Aline-Quirosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2254,13 +2278,13 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/hering.com.br%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Psicloga%20Aline%20Quirosa%2C%20So%20Paulo%20%282026%29%20sao%20paulo</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da hering.com.br aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Psicloga Aline Quirosa, So Paulo (2026) aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2270,29 +2294,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a hering.com.br?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Psicloga Aline Quirosa, So Paulo (2026)?</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20hering.com.br%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psicloga%20Aline%20Quirosa%2C%20So%20Paulo%20%282026%29%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20hering.com.br%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psicloga%20Aline%20Quirosa%2C%20So%20Paulo%20%282026%29%3F</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Web site created using create-react-app</t>
+          <t>Clnica Psico Self</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Web site created using create-react-app</t>
+          <t>Clínica Psico Self – Psicologia e Bem Estar na Zona Norte ...</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2307,17 +2331,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Web site created using create-react-app......</t>
+          <t>UNIDADE I - PSI Atendimento psicológico Parque Domingos Luís, 126 Jd. São Paulo UNIDADE II - PICS Te...</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SITE FORA DO AR / LINK QUEBRADO 🚨</t>
+          <t>SITE ATIVO 📱</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://cadunico.dataprev.gov.br/</t>
+          <t>https://www.clinicapsicoself.com.br/</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2328,13 +2352,13 @@
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Web%20site%20created%20using%20create-react-app%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Clnica%20Psico%20Self%20sao%20paulo</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Web site created using create-react-app aí em Sao paulo no Google e fui tentar acessar o site de vocês e vi que está fora do ar.
+Vi o perfil da Clnica Psico Self aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2344,29 +2368,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Web site created using create-react-app?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Clnica Psico Self?</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Web%20site%20created%20using%20create-react-app%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20fui%20tentar%20acessar%20o%20site%20de%20voc%C3%AAs%20e%20vi%20que%20est%C3%A1%20fora%20do%20ar.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clnica%20Psico%20Self%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Web%20site%20created%20using%20create-react-app%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clnica%20Psico%20Self%3F</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Bar Recanto de Santa Barbara em So Paulo, SP.</t>
+          <t>Bem Estar Psicologia</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Bar Recanto de Santa Barbara em São Paulo, SP...</t>
+          <t>Bem Estar Psicologia | Psicólogos e Fonoaudiólogo em São ...</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2381,7 +2405,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>O endereço de sua sede está localizada na Rua Callixto, 171 - Cidade Satelite Santa Barbara, Sao Pau...</t>
+          <t>Clínica de Psicologia e Fonoaudiologia na Zona Norte de São Paulo. Atendimento presencial e online p...</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2391,24 +2415,28 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.econodata.com.br/consulta-empresa/03523129000172-bar-e-restaurante-recanto-de-santa-barbara-ltda</t>
+          <t>https://www.bemestarpsicologia.com.br/</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(SA) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(11) 3867-8970</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>551138678970</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Bar%20Recanto%20de%20Santa%20Barbara%20em%20So%20Paulo%2C%20SP.%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Bem%20Estar%20Psicologia%20sao%20paulo</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Bar Recanto de Santa Barbara em So Paulo, SP. aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Bem Estar Psicologia aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2418,29 +2446,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Bar Recanto de Santa Barbara em So Paulo, SP.?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Bem Estar Psicologia?</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Bar%20Recanto%20de%20Santa%20Barbara%20em%20So%20Paulo%2C%20SP.%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/551138678970?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Bem%20Estar%20Psicologia%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Bar%20Recanto%20de%20Santa%20Barbara%20em%20So%20Paulo%2C%20SP.%3F</t>
+          <t>https://wa.me/551138678970?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Bem%20Estar%20Psicologia%3F</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Mapas de muestra de Aguas de Santa Barbara ge</t>
+          <t>Incio</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mapas de muestra de Aguas de Santa Barbara generados con la...</t>
+          <t>Início - Instituto de Psiquiatria Paulista</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2455,7 +2483,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Muestras de recorte de mapas Aguas de Santa Barbara (Sao Paulo)-1....</t>
+          <t>Contamos com uma equipe de mais de 100 especialistas em psiquiatria, neurologia, neuropsicologia e p...</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2465,24 +2493,28 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://tools.paintmaps.com/es/recorte-de-mapa/BR/4-102061001/muestras</t>
+          <t>https://psiquiatriapaulista.com.br/</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(SA) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(22) 99977-0015</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5522999770015</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Mapas%20de%20muestra%20de%20Aguas%20de%20Santa%20Barbara%20ge%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Incio%20sao%20paulo</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Mapas de muestra de Aguas de Santa Barbara ge aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Incio aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2492,68 +2524,1584 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Mapas de muestra de Aguas de Santa Barbara ge?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Incio?</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Mapas%20de%20muestra%20de%20Aguas%20de%20Santa%20Barbara%20ge%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5522999770015?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Incio%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Mapas%20de%20muestra%20de%20Aguas%20de%20Santa%20Barbara%20ge%3F</t>
+          <t>https://wa.me/5522999770015?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Incio%3F</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Clnica de Psiquiatria e Psicologia Vida Menta</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Clínica de Psiquiatria e Psicologia Vida Mental By CREMED</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Sao paulo</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Centro / Região</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Psicologia Clínica Tratamentos de psicoterapia para a solução de problemas de saúde mental e promoçã...</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>SITE ATIVO 📱</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://vidamentalbycremed.com.br/</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(11) 4114-0019</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>551141140019</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/Clnica%20de%20Psiquiatria%20e%20Psicologia%20Vida%20Menta%20sao%20paulo</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
+Vi o perfil da Clnica de Psiquiatria e Psicologia Vida Menta aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
+Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
+A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
+Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
+Posso te mandar a prévia demonstrativa que fiz para a Clnica de Psiquiatria e Psicologia Vida Menta?</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>https://wa.me/551141140019?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clnica%20de%20Psiquiatria%20e%20Psicologia%20Vida%20Menta%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>https://wa.me/551141140019?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clnica%20de%20Psiquiatria%20e%20Psicologia%20Vida%20Menta%3F</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>JalaLive</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>JalaLive</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Sao paulo</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Centro / Região</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>LIVE Babak 2 Brazilian Serie D Esporte Clube São José Porto Alegre Esporte......</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>SITE ATIVO 📱</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.jala7mjm.com/</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(SA) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/JalaLive%20sao%20paulo</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
+Vi o perfil da JalaLive aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
+Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
+A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
+Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
+Posso te mandar a prévia demonstrativa que fiz para a JalaLive?</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20JalaLive%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20JalaLive%3F</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Detran</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Detran</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Sao paulo</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Centro / Região</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Você não fez login, ou sua sessão expirou. Redirecionando para a página de login....</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>SITE ATIVO 📱</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.detran.sp.gov.br/session_timeout.do</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(11) 2178-9494</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>551121789494</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/Detran%20sao%20paulo</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
+Vi o perfil da Detran aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
+Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
+A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
+Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
+Posso te mandar a prévia demonstrativa que fiz para a Detran?</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>https://wa.me/551121789494?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Detran%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>https://wa.me/551121789494?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Detran%3F</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Link to facebook.com</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Link to facebook.com</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Sao paulo</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Centro / Região</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>The site owner hides the web page description....</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>SEM SITE PRÓPRIO (OPORTUNIDADE 🔥)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Sem Site Cadastrado</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(SA) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/Link%20to%20facebook.com%20sao%20paulo</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
+Vi o perfil da Link to facebook.com aí em Sao paulo no Google e vi que vocês ainda não têm um site próprio para celular.
+Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
+Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
+A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
+Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
+Posso te mandar a prévia demonstrativa que fiz para a Link to facebook.com?</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Link%20to%20facebook.com%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Link%20to%20facebook.com%3F</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Elaine ferreira psicloga clnica, psicologo...</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Elaine ferreira psicóloga clínica, psicologo...</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Sao paulo</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Centro / Região</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Bairro: Freguesia do Ó. Cidade: São Paulo. Estado: SP.Sua mensagem será enviada para nossa equipe e ...</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>SITE ATIVO 📱</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.terapyas.com.br/sobre/elaine-ferreira-psicologa-clinica-psicologo-atendimento-psicologico-e-terapia-sao-paulo-sp</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(11) 97622-2228</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>5511976222228</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/Elaine%20ferreira%20psicloga%20clnica%2C%20psicologo...%20sao%20paulo</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
+Vi o perfil da Elaine ferreira psicloga clnica, psicologo... aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
+Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
+A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
+Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
+Posso te mandar a prévia demonstrativa que fiz para a Elaine ferreira psicloga clnica, psicologo...?</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>https://wa.me/5511976222228?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Elaine%20ferreira%20psicloga%20clnica%2C%20psicologo...%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>https://wa.me/5511976222228?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Elaine%20ferreira%20psicloga%20clnica%2C%20psicologo...%3F</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Pmela Dauzcuk Psiclogo, So Paulo</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Pâmela Dauzcuk Psicólogo, São Paulo - Agende uma consulta ...</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Sao paulo</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Centro / Região</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Economize tempo agendando um horário online com Pâmela Dauzcuk, Psicólogo em São Paulo. Leia os come...</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>SEM SITE (OPORTUNIDADE QUENTE 🔥)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Sem Site Cadastrado</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(SA) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/Pmela%20Dauzcuk%20Psiclogo%2C%20So%20Paulo%20sao%20paulo</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
+Vi o perfil da Pmela Dauzcuk Psiclogo, So Paulo aí em Sao paulo no Google e vi que vocês ainda não têm um site próprio para celular.
+Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
+Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
+A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
+Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
+Posso te mandar a prévia demonstrativa que fiz para a Pmela Dauzcuk Psiclogo, So Paulo?</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Pmela%20Dauzcuk%20Psiclogo%2C%20So%20Paulo%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Pmela%20Dauzcuk%20Psiclogo%2C%20So%20Paulo%3F</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Terapia online com psiclogos disponveis 24h p</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Terapia online com psicólogos disponíveis 24h por dia | Zenklub</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Sao paulo</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Centro / Região</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Estamos sempre com você. Todo dia e a qualquer hora, nossos especialistas estarão disponíveis para a...</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>SITE ATIVO 📱</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://zenklub.com.br/</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(SA) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/Terapia%20online%20com%20psiclogos%20disponveis%2024h%20p%20sao%20paulo</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
+Vi o perfil da Terapia online com psiclogos disponveis 24h p aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
+Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
+A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
+Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
+Posso te mandar a prévia demonstrativa que fiz para a Terapia online com psiclogos disponveis 24h p?</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Terapia%20online%20com%20psiclogos%20disponveis%2024h%20p%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Terapia%20online%20com%20psiclogos%20disponveis%2024h%20p%3F</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Ofertas e Cupons de</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Ofertas e Cupons de Desconto para Porto Alegre, Gramado e Mais!</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Sao paulo</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Centro / Região</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Central de atendimento. Icone WhatsApp....</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>SITE ATIVO 📱</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.tcheofertas.com.br/</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(SA) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/Ofertas%20e%20Cupons%20de%20sao%20paulo</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
+Vi o perfil da Ofertas e Cupons de aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
+Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
+A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
+Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
+Posso te mandar a prévia demonstrativa que fiz para a Ofertas e Cupons de?</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Ofertas%20e%20Cupons%20de%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Ofertas%20e%20Cupons%20de%3F</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Super Portal</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Super Portal</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Sao paulo</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Centro / Região</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Marcação consulta/exame Atendimento....</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>SITE ATIVO 📱</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://portal-beneficiario.hapvida.com.br/</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(SA) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/Super%20Portal%20sao%20paulo</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
+Vi o perfil da Super Portal aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
+Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
+A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
+Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
+Posso te mandar a prévia demonstrativa que fiz para a Super Portal?</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Super%20Portal%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Super%20Portal%3F</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Cotiza Vuelos, Paquetes, Hoteles y Autos</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Cotiza Vuelos, Paquetes, Hoteles y Autos | LATAM en Chile</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Sao paulo</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Centro / Região</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Conoce tus derechos. Reorganización financiera / Capítulo 11. Intercambio de slots Sao Paulo (GRU)....</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>SITE FORA DO AR / LINK QUEBRADO 🚨</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.latamairlines.com/</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(SA) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/Cotiza%20Vuelos%2C%20Paquetes%2C%20Hoteles%20y%20Autos%20sao%20paulo</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
+Vi o perfil da Cotiza Vuelos, Paquetes, Hoteles y Autos aí em Sao paulo no Google e fui tentar acessar o site de vocês e vi que está fora do ar.
+Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
+Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
+A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
+Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
+Posso te mandar a prévia demonstrativa que fiz para a Cotiza Vuelos, Paquetes, Hoteles y Autos?</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Cotiza%20Vuelos%2C%20Paquetes%2C%20Hoteles%20y%20Autos%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20fui%20tentar%20acessar%20o%20site%20de%20voc%C3%AAs%20e%20vi%20que%20est%C3%A1%20fora%20do%20ar.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Cotiza%20Vuelos%2C%20Paquetes%2C%20Hoteles%20y%20Autos%3F</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PSI Site do CRP SP</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>PSI Site do CRP SP</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Sao paulo</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Centro / Região</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Para atendimento presencial, preferencialmente realize o agendamento prévio. Para demais consultas, ...</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>SITE ATIVO 📱</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.crpsp.org/</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(11) 3065-9494</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>551130659494</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/PSI%20Site%20do%20CRP%20SP%20sao%20paulo</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
+Vi o perfil da PSI Site do CRP SP aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
+Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
+A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
+Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
+Posso te mandar a prévia demonstrativa que fiz para a PSI Site do CRP SP?</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>https://wa.me/551130659494?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20PSI%20Site%20do%20CRP%20SP%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>https://wa.me/551130659494?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20PSI%20Site%20do%20CRP%20SP%3F</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Portal oficial do Governo da Bahia com servio</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Portal oficial do Governo da Bahia com serviços públicos online</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Sao paulo</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Centro / Região</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Portal oficial do Governo da Bahia com serviços públicos online......</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>SITE ATIVO 📱</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.ba.gov.br/</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(SA) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/Portal%20oficial%20do%20Governo%20da%20Bahia%20com%20servio%20sao%20paulo</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
+Vi o perfil da Portal oficial do Governo da Bahia com servio aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
+Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
+A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
+Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
+Posso te mandar a prévia demonstrativa que fiz para a Portal oficial do Governo da Bahia com servio?</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Portal%20oficial%20do%20Governo%20da%20Bahia%20com%20servio%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Portal%20oficial%20do%20Governo%20da%20Bahia%20com%20servio%3F</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Barbearia em So Paulo</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Barbearia em São Paulo - perto de mim - Cabeleireiro ...</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Sao paulo</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Centro / Região</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Para evitar isso, use os mecanismos de localização do Booksy e encontre os lugares mais próximos da ...</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>SITE ATIVO 📱</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://booksy.com/pt-br/s/barbearias/1047773_sao-paulo</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(11) 94990-8390</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>5511949908390</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/Barbearia%20em%20So%20Paulo%20sao%20paulo</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
+Vi o perfil da Barbearia em So Paulo aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
+Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
+A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
+Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
+Posso te mandar a prévia demonstrativa que fiz para a Barbearia em So Paulo?</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>https://wa.me/5511949908390?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Barbearia%20em%20So%20Paulo%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>https://wa.me/5511949908390?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Barbearia%20em%20So%20Paulo%3F</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>As 10 melhores barbearias de So Paulo</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>As 10 melhores barbearias de São Paulo - O melhor de São Paulo</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Sao paulo</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Centro / Região</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Selecionamos as melhores barbearias SP que se sobressaem pelo atendimento, qualidade dos serviços, s...</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>SITE ATIVO 📱</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.melhoressaopaulo.com/barbearias/</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(SA) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/As%2010%20melhores%20barbearias%20de%20So%20Paulo%20sao%20paulo</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
+Vi o perfil da As 10 melhores barbearias de So Paulo aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
+Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
+A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
+Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
+Posso te mandar a prévia demonstrativa que fiz para a As 10 melhores barbearias de So Paulo?</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20As%2010%20melhores%20barbearias%20de%20So%20Paulo%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20As%2010%20melhores%20barbearias%20de%20So%20Paulo%3F</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Barbearia Hermanos</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Barbearia Hermanos - Barbearia em São Paulo, Barbeiro ...</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Sao paulo</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Centro / Região</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Na Barbearia Hermanos, acreditamos que o cuidado com a aparência vai muito além de um simples corte ...</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>SITE ATIVO 📱</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://barbeariahermanos.com.br/</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(11) 3333-5704</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>551133335704</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/Barbearia%20Hermanos%20sao%20paulo</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
+Vi o perfil da Barbearia Hermanos aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
+Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
+A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
+Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
+Posso te mandar a prévia demonstrativa que fiz para a Barbearia Hermanos?</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>https://wa.me/551133335704?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Barbearia%20Hermanos%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>https://wa.me/551133335704?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Barbearia%20Hermanos%3F</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Barbearia Tarantino</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Barbearia Tarantino | www.barbeariatarantino.com.br | São Paulo</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Sao paulo</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Centro / Região</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Inaugurada em 2015, a Barbearia Tarantino tem uma pegada clássica sem perder a modernidade. Em 2016,...</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>SITE ATIVO 📱</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.barbeariatarantino.com.br/</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(11) 3384-5530</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>551133845530</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/Barbearia%20Tarantino%20sao%20paulo</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
+Vi o perfil da Barbearia Tarantino aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
+Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
+A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
+Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
+Posso te mandar a prévia demonstrativa que fiz para a Barbearia Tarantino?</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>https://wa.me/551133845530?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Barbearia%20Tarantino%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>https://wa.me/551133845530?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Barbearia%20Tarantino%3F</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Bar Recanto de Santa Barbara em So Paulo, SP.</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Bar Recanto de Santa Barbara em São Paulo, SP...</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Sao paulo</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Centro / Região</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>O endereço de sua sede está localizada na Rua Callixto, 171 - Cidade Satelite Santa Barbara, Sao Pau...</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>SITE ATIVO 📱</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.econodata.com.br/consulta-empresa/03523129000172-bar-e-restaurante-recanto-de-santa-barbara-ltda</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(SA) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/Bar%20Recanto%20de%20Santa%20Barbara%20em%20So%20Paulo%2C%20SP.%20sao%20paulo</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
+Vi o perfil da Bar Recanto de Santa Barbara em So Paulo, SP. aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
+Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
+A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
+Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
+Posso te mandar a prévia demonstrativa que fiz para a Bar Recanto de Santa Barbara em So Paulo, SP.?</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Bar%20Recanto%20de%20Santa%20Barbara%20em%20So%20Paulo%2C%20SP.%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Bar%20Recanto%20de%20Santa%20Barbara%20em%20So%20Paulo%2C%20SP.%3F</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Brasil Rugby vs Barbarians</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Brasil Rugby vs Barbarians - São Paulo SP - 20/11/2019... - YouTu</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Sao paulo</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Centro / Região</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>© 2026 Google LLC....</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>SEM SITE PRÓPRIO (OPORTUNIDADE 🔥)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Sem Site Cadastrado</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(11) 98104-2508</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5511981042508</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/Brasil%20Rugby%20vs%20Barbarians%20sao%20paulo</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
+Vi o perfil da Brasil Rugby vs Barbarians aí em Sao paulo no Google e vi que vocês ainda não têm um site próprio para celular.
+Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
+Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
+A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
+Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
+Posso te mandar a prévia demonstrativa que fiz para a Brasil Rugby vs Barbarians?</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>https://wa.me/5511981042508?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Brasil%20Rugby%20vs%20Barbarians%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>https://wa.me/5511981042508?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Brasil%20Rugby%20vs%20Barbarians%3F</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>JOSE LIMA FARIAS 02266642529</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>JOSE LIMA FARIAS 02266642529 — CNPJ... | Sr. Watson</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Sao paulo</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Centro / Região</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Avenida sapopemba, 16255, cidade satelite santa barbara, sao paulo/SP, 08330-180. Abrir no Google Ma...</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>SITE ATIVO 📱</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://srwatson.io/empresa/jose-lima-farias-02266642529-34905124000138</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(02) 2666-4252</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>550226664252</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/JOSE%20LIMA%20FARIAS%2002266642529%20sao%20paulo</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
+Vi o perfil da JOSE LIMA FARIAS 02266642529 aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
+Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
+A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
+Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
+Posso te mandar a prévia demonstrativa que fiz para a JOSE LIMA FARIAS 02266642529?</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>https://wa.me/550226664252?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20JOSE%20LIMA%20FARIAS%2002266642529%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>https://wa.me/550226664252?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20JOSE%20LIMA%20FARIAS%2002266642529%3F</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Mapas de muestra de Aguas de Santa Barbara ge</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Mapas de muestra de Aguas de Santa Barbara generados con la...</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Sao paulo</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Centro / Região</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Muestras de recorte de mapas Aguas de Santa Barbara (Sao Paulo)-1....</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>SITE ATIVO 📱</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://tools.paintmaps.com/es/recorte-de-mapa/BR/4-102061001/muestras</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(SA) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/Mapas%20de%20muestra%20de%20Aguas%20de%20Santa%20Barbara%20ge%20sao%20paulo</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
+Vi o perfil da Mapas de muestra de Aguas de Santa Barbara ge aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
+Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
+A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
+Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
+Posso te mandar a prévia demonstrativa que fiz para a Mapas de muestra de Aguas de Santa Barbara ge?</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Mapas%20de%20muestra%20de%20Aguas%20de%20Santa%20Barbara%20ge%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Mapas%20de%20muestra%20de%20Aguas%20de%20Santa%20Barbara%20ge%3F</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>FreeGuessr</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>FreeGuessr - Free GeoGuessr Alternative</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Sao paulo</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Centro / Região</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Sao paulo</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Centro / Região</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
         <is>
           <t>Free GeoGuessr game alternative with unlimited play. Play multiplayer GeoGuessr-like games with frie...</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>SITE ATIVO 📱</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>https://freeguessr.com/</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>(SA) 98877-6655</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/FreeGuessr%20sao%20paulo</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
 Vi o perfil da FreeGuessr aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
@@ -2561,7 +4109,7 @@
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
@@ -2569,12 +4117,12 @@
 Posso te mandar a prévia demonstrativa que fiz para a FreeGuessr?</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20FreeGuessr%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20FreeGuessr%3F</t>
         </is>

--- a/leads_psicologo_sao_paulo.xlsx
+++ b/leads_psicologo_sao_paulo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N49"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,12 +569,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Psiclogo So Paulo Laura Ciasca Mandaqui...</t>
+          <t>CNPJ 46.506.509/0001-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Psicólogo São Paulo Laura Ciasca Mandaqui... | Bendito Guia</t>
+          <t>CNPJ 46.506.509/0001-01 - psicologo celso silva | CNPJ go!</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -589,17 +589,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>A busca por um psicólogo em São Paulo pode ser um desafio, mas com a Psicólogo São Paulo Laura Ciasc...</t>
+          <t>Consulte dados de PSICOLOGO CELSO SILVA — CNPJ 46.506.509/0001-01. Situação: Ativa. SAO PAULO/SP. Só...</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SITE ATIVO 📱</t>
+          <t>SITE FORA DO AR / LINK QUEBRADO 🚨</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.benditoguia.com.br/empresa/psicologo-sao-paulo-laura-ciasca-mandaqui</t>
+          <t>https://cnpjgo.com.br/cnpj/46506509000101</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -610,13 +610,13 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Psiclogo%20So%20Paulo%20Laura%20Ciasca%20Mandaqui...%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/CNPJ%2046.506.509/0001-01%20sao%20paulo</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Psiclogo So Paulo Laura Ciasca Mandaqui... aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da CNPJ 46.506.509/0001-01 aí em Sao paulo no Google e fui tentar acessar o site de vocês e vi que está fora do ar.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -626,29 +626,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Psiclogo So Paulo Laura Ciasca Mandaqui...?</t>
+Posso te mandar a prévia demonstrativa que fiz para a CNPJ 46.506.509/0001-01?</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psiclogo%20So%20Paulo%20Laura%20Ciasca%20Mandaqui...%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20CNPJ%2046.506.509/0001-01%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20fui%20tentar%20acessar%20o%20site%20de%20voc%C3%AAs%20e%20vi%20que%20est%C3%A1%20fora%20do%20ar.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psiclogo%20So%20Paulo%20Laura%20Ciasca%20Mandaqui...%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20CNPJ%2046.506.509/0001-01%3F</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Psicloga Maristela Vallim Botari em So Paulo</t>
+          <t>Psiclogo em So Paulo</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Psicóloga Maristela Vallim Botari em São Paulo</t>
+          <t>Psicólogo em São Paulo - PsyCare</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>[Psicóloga SP] Responde: Perguntas frequentes sobre Psicólogos e Terapia. Pesquisar no site. Página ...</t>
+          <t>Psicólogo em são paulo, você está dando um passo importante em direção ao autocuidado e ao desenvolv...</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.psicologaresponde.com.br/2023/10/psicologa-maristela-vallim-botari-em.html</t>
+          <t>https://www.psycare.com.br/psicologo-sao-paulo</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -684,13 +684,13 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Psicloga%20Maristela%20Vallim%20Botari%20em%20So%20Paulo%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Psiclogo%20em%20So%20Paulo%20sao%20paulo</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Psicloga Maristela Vallim Botari em So Paulo aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Psiclogo em So Paulo aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -700,29 +700,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Psicloga Maristela Vallim Botari em So Paulo?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Psiclogo em So Paulo?</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psicloga%20Maristela%20Vallim%20Botari%20em%20So%20Paulo%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psiclogo%20em%20So%20Paulo%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psicloga%20Maristela%20Vallim%20Botari%20em%20So%20Paulo%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psiclogo%20em%20So%20Paulo%3F</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Vagas de Psiclogo em So Paulo, SP</t>
+          <t>Psicloga Aline Quirosa, So Paulo (2026)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Vagas de Psicólogo em São Paulo, SP | Indeed</t>
+          <t>Psicóloga Aline Quirosa, São Paulo (2026)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vagas: psicólogo - São Paulo, SP. Ordenar por: relevância - data.São Paulo, SP. Conhecer diagnóstico...</t>
+          <t>Brasil. São Paulo, SP. Psicóloga Aline Quirosa....</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -747,24 +747,28 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://br.indeed.com/q-psicólogo-l-são-paulo,-sp-vagas.html</t>
+          <t>https://www.findhealthclinics.org/BR/São-Paulo/103266911851448/Psicóloga-Aline-Quirosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(SA) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(52) 8293-9100</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>555282939100</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Vagas%20de%20Psiclogo%20em%20So%20Paulo%2C%20SP%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Psicloga%20Aline%20Quirosa%2C%20So%20Paulo%20%282026%29%20sao%20paulo</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Vagas de Psiclogo em So Paulo, SP aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Psicloga Aline Quirosa, So Paulo (2026) aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -774,29 +778,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Vagas de Psiclogo em So Paulo, SP?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Psicloga Aline Quirosa, So Paulo (2026)?</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Vagas%20de%20Psiclogo%20em%20So%20Paulo%2C%20SP%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/555282939100?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psicloga%20Aline%20Quirosa%2C%20So%20Paulo%20%282026%29%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Vagas%20de%20Psiclogo%20em%20So%20Paulo%2C%20SP%3F</t>
+          <t>https://wa.me/555282939100?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psicloga%20Aline%20Quirosa%2C%20So%20Paulo%20%282026%29%3F</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Psiclogo em So Paulo</t>
+          <t>Psicologo felipe faccioli</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Psicólogo em São Paulo - PsyCare</t>
+          <t>Psicologo felipe faccioli - CNPJ 63.510.039/0001-79</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -811,7 +815,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Psicólogo em são paulo, você está dando um passo importante em direção ao autocuidado e ao desenvolv...</t>
+          <t>Consulte o CNPJ 63.510.039/0001-79 da empresa PSICOLOGO FELIPE FACCIOLI (FELIPE FACCIOLI DE SOUZA LT...</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -821,24 +825,28 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.psycare.com.br/psicologo-sao-paulo</t>
+          <t>https://cnpj.today/63510039000179</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(SA) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(41) 9788-0145</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>554197880145</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Psiclogo%20em%20So%20Paulo%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Psicologo%20felipe%20faccioli%20sao%20paulo</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Psiclogo em So Paulo aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Psicologo felipe faccioli aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -848,17 +856,17 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Psiclogo em So Paulo?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Psicologo felipe faccioli?</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psiclogo%20em%20So%20Paulo%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/554197880145?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psicologo%20felipe%20faccioli%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psiclogo%20em%20So%20Paulo%3F</t>
+          <t>https://wa.me/554197880145?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psicologo%20felipe%20faccioli%3F</t>
         </is>
       </c>
     </row>
@@ -1017,12 +1025,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Psicloga Brooklin</t>
+          <t>Gustavo Cicilini</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Psicóloga Brooklin | Consultório Psicólogos Berrini</t>
+          <t>Gustavo Cicilini - Psicólogo e Consultor de Pessoas | LinkedIn</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1037,7 +1045,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Psicóloga Brooklin na Zona Sul. O consultório Psicólogos Berrini tem mais de 15 anos de tradição no ...</t>
+          <t>Psicólogo e executivo com mais de 25 anos de experiência em Recursos Humanos em… · Experiência: Psic...</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1047,28 +1055,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.psicologosberrini.com.br/</t>
+          <t>https://br.linkedin.com/in/gustavocicilini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(11) 5102-3493</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>551151023493</t>
-        </is>
-      </c>
+          <t>(SA) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Psicloga%20Brooklin%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Gustavo%20Cicilini%20sao%20paulo</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Psicloga Brooklin aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Gustavo Cicilini aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1078,17 +1082,17 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Psicloga Brooklin?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Gustavo Cicilini?</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://wa.me/551151023493?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psicloga%20Brooklin%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Gustavo%20Cicilini%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://wa.me/551151023493?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psicloga%20Brooklin%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Gustavo%20Cicilini%3F</t>
         </is>
       </c>
     </row>
@@ -1130,10 +1134,14 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(SA) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(11) 99333-8208</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5511993338208</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/Psiclogo%20Clnico%20Particular%20em%20Perdizes%20sao%20paulo</t>
@@ -1157,24 +1165,24 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psiclogo%20Clnico%20Particular%20em%20Perdizes%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5511993338208?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psiclogo%20Clnico%20Particular%20em%20Perdizes%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psiclogo%20Clnico%20Particular%20em%20Perdizes%3F</t>
+          <t>https://wa.me/5511993338208?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psiclogo%20Clnico%20Particular%20em%20Perdizes%3F</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Psicologo Transpessoal Em Perdizes</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Portal - Detran-SP</t>
+          <t>Psicologo Transpessoal Em Perdizes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1189,7 +1197,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>O novo Portal do Detran-SP feito pra você! Mais fácil, rápido e digital. Pra você não perder tempo c...</t>
+          <t>Psicologo Transpessoal em Perdizes Psicoterapia, autoconhecimento, prevenção e tratamento de distúrb...</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1199,24 +1207,28 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.detran.sp.gov.br/</t>
+          <t>https://www.cuiket.com.br/empresa/psicologo-transpessoal-em-perdizes_5001176.html</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(SA) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(11) 2368-1764</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>551123681764</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Portal%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Psicologo%20Transpessoal%20Em%20Perdizes%20sao%20paulo</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Portal aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Psicologo Transpessoal Em Perdizes aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1226,17 +1238,17 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Portal?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Psicologo Transpessoal Em Perdizes?</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Portal%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/551123681764?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psicologo%20Transpessoal%20Em%20Perdizes%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Portal%3F</t>
+          <t>https://wa.me/551123681764?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psicologo%20Transpessoal%20Em%20Perdizes%3F</t>
         </is>
       </c>
     </row>
@@ -1317,12 +1329,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Terapia e Psicloga Online por</t>
+          <t>VLOG vivendo em Sao Paulo: brunch, brech &amp; bo</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Terapia e Psicóloga Online por whatsapp ☆</t>
+          <t>VLOG vivendo em Sao Paulo: brunch, brechó &amp; boteco - YouTube</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1337,17 +1349,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>A terapia online pode ser realizada via WhatsApp ou plataformas específicas de videoconferência, gar...</t>
+          <t>О сервисе Прессе Авторские права Связаться с нами Авторам Рекламодателям......</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SITE ATIVO 📱</t>
+          <t>SEM SITE PRÓPRIO (OPORTUNIDADE 🔥)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.psicologiasemfronteiras.com.br/p/psicologa-online-via-skype-ou-whatsapp.html</t>
+          <t>Sem Site Cadastrado</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1358,13 +1370,13 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Terapia%20e%20Psicloga%20Online%20por%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/VLOG%20vivendo%20em%20Sao%20Paulo%3A%20brunch%2C%20brech%20%26%20bo%20sao%20paulo</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Terapia e Psicloga Online por aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da VLOG vivendo em Sao Paulo: brunch, brech &amp; bo aí em Sao paulo no Google e vi que vocês ainda não têm um site próprio para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1374,17 +1386,17 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Terapia e Psicloga Online por?</t>
+Posso te mandar a prévia demonstrativa que fiz para a VLOG vivendo em Sao Paulo: brunch, brech &amp; bo?</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Terapia%20e%20Psicloga%20Online%20por%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20VLOG%20vivendo%20em%20Sao%20Paulo%3A%20brunch%2C%20brech%20%26%20bo%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Terapia%20e%20Psicloga%20Online%20por%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20VLOG%20vivendo%20em%20Sao%20Paulo%3A%20brunch%2C%20brech%20%26%20bo%3F</t>
         </is>
       </c>
     </row>
@@ -1469,12 +1481,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Psiclogo Terapeuta Preo Anlia Franco</t>
+          <t>Consultrio Psiclogos Berrini</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Psicólogo Terapeuta Preço Anália Franco - Psico Plus</t>
+          <t>Consultório Psicólogos Berrini - Mental Health Clinic in Itaim Bi</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1489,7 +1501,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Clínicas de psicologia em São Paulo: Encontre o apoio que você precisa para sua saúde mental.onde en...</t>
+          <t>consultório psicólogos berrini itaim bibi são paulo.Consultório Psicólogos Berrini. Rua Alcides Rica...</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1499,28 +1511,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.clinicapsicoplus.com.br/terapia/terapia-em-sao-paulo/psicologo-terapeuta-preco-analia-franco</t>
+          <t>https://foursquare.com/v/consultório-psicólogos-berrini/562623d9498e934035665ab1</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(14) 3841-2400</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>551438412400</t>
-        </is>
-      </c>
+          <t>(SA) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Psiclogo%20Terapeuta%20Preo%20Anlia%20Franco%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Consultrio%20Psiclogos%20Berrini%20sao%20paulo</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Psiclogo Terapeuta Preo Anlia Franco aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Consultrio Psiclogos Berrini aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1530,29 +1538,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Psiclogo Terapeuta Preo Anlia Franco?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Consultrio Psiclogos Berrini?</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>https://wa.me/551438412400?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psiclogo%20Terapeuta%20Preo%20Anlia%20Franco%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Consultrio%20Psiclogos%20Berrini%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://wa.me/551438412400?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psiclogo%20Terapeuta%20Preo%20Anlia%20Franco%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Consultrio%20Psiclogos%20Berrini%3F</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>36 avaliaes sobre Psicloga Alessa Brando Latb</t>
+          <t>Psiclogo Terapeuta Santana</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>36 avaliações sobre Psicóloga Alessa Brandão Latíbulo Consultório</t>
+          <t>Psicólogo Terapeuta Santana - Psico Plus</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1567,7 +1575,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Avaliações » Psicologo » São Paulo » Sao paulo » Psicologa alessa brandao latib.(Psicólogo) em São P...</t>
+          <t>Faça seu orçamento por Whatsapp. Rua Gomes de Carvalho 768, 2º andar - São Paulo - SP.onde encontrar...</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1577,28 +1585,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://avaliacoesbrasil.com/psicologo/sao-paulo/psicologa-alessa-brandao-latib/</t>
+          <t>https://www.clinicapsicoplus.com.br/terapia/terapia-em-sao-paulo/psicologo-terapeuta-santana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(19) 99997-0207</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5519999970207</t>
-        </is>
-      </c>
+          <t>(SA) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/36%20avaliaes%20sobre%20Psicloga%20Alessa%20Brando%20Latb%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Psiclogo%20Terapeuta%20Santana%20sao%20paulo</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da 36 avaliaes sobre Psicloga Alessa Brando Latb aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Psiclogo Terapeuta Santana aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1608,17 +1612,17 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a 36 avaliaes sobre Psicloga Alessa Brando Latb?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Psiclogo Terapeuta Santana?</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://wa.me/5519999970207?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%2036%20avaliaes%20sobre%20Psicloga%20Alessa%20Brando%20Latb%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psiclogo%20Terapeuta%20Santana%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://wa.me/5519999970207?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%2036%20avaliaes%20sobre%20Psicloga%20Alessa%20Brando%20Latb%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psiclogo%20Terapeuta%20Santana%3F</t>
         </is>
       </c>
     </row>
@@ -1699,12 +1703,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Psicologa Online: Acolhimento Humanizado</t>
+          <t>Terappia</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Psicologa Online: Acolhimento Humanizado</t>
+          <t>Terappia - Psicologia Online. Consultas a partir de R$ 40 ...</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1719,38 +1723,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Psicologa online por whatsapp, ou presencial na Bela vista. Agende sua sessão com acolhimento humani...</t>
+          <t>Terapia online com psicólogos via WhatsApp. Consultas a partir de R$ 40. Encontre o seu psicólogo on...</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SITE FORA DO AR (ERRO 404) 🚨</t>
+          <t>SEM SITE PRÓPRIO (OPORTUNIDADE 🔥)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.psicologaresponde.com.br/2014/12/psicologo-sp-online_28.html</t>
+          <t>Sem Site Cadastrado</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(11) 2661-5000</t>
+          <t>(21) 99985-0091</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>551126615000</t>
+          <t>5521999850091</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Psicologa%20Online%3A%20Acolhimento%20Humanizado%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Terappia%20sao%20paulo</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Psicologa Online: Acolhimento Humanizado aí em Sao paulo no Google e fui tentar acessar o site de vocês e vi que está fora do ar.
+Vi o perfil da Terappia aí em Sao paulo no Google e vi que vocês ainda não têm um site próprio para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1760,17 +1764,17 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Psicologa Online: Acolhimento Humanizado?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Terappia?</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>https://wa.me/551126615000?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psicologa%20Online%3A%20Acolhimento%20Humanizado%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20fui%20tentar%20acessar%20o%20site%20de%20voc%C3%AAs%20e%20vi%20que%20est%C3%A1%20fora%20do%20ar.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5521999850091?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Terappia%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://wa.me/551126615000?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psicologa%20Online%3A%20Acolhimento%20Humanizado%3F</t>
+          <t>https://wa.me/5521999850091?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Terappia%3F</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1801,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ex-diretor de futebol do São Paulo....</t>
+          <t>O mecanismo de busca que ajuda a localizar exatamente o que você procura. Busque as informações, víd...</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1855,12 +1859,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>OKESTREAM</t>
+          <t>Detran</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>OKESTREAM - Nonton Bola Online Gratis Tanpa Buffering</t>
+          <t>Detran</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1875,7 +1879,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>São Paulo....</t>
+          <t>Você não fez login, ou sua sessão expirou. Redirecionando para a página de login....</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1885,24 +1889,28 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://okestream.yachts/</t>
+          <t>https://www.detran.sp.gov.br/session_timeout.do</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(SA) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(80) 0905-5555</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>558009055555</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/OKESTREAM%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Detran%20sao%20paulo</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da OKESTREAM aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Detran aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1912,29 +1920,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a OKESTREAM?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Detran?</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20OKESTREAM%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/558009055555?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Detran%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20OKESTREAM%3F</t>
+          <t>https://wa.me/558009055555?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Detran%3F</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Terappia</t>
+          <t>OKESTREAM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Terappia - Psicologia Online. Consultas a partir de R$ 40 ...</t>
+          <t>OKESTREAM - Nonton Bola Online Gratis Tanpa Buffering</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1949,38 +1957,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Terapia online com psicólogos via WhatsApp. Consultas a partir de R$ 40. Encontre o seu psicólogo on...</t>
+          <t>Okestream menyediakan live streaming sepakbola terlengkap dan terbaik se Indonesia. Nonton bola sema...</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SEM SITE PRÓPRIO (OPORTUNIDADE 🔥)</t>
+          <t>SITE ATIVO 📱</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sem Site Cadastrado</t>
+          <t>https://okestream.yachts/</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(21) 99985-0091</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5521999850091</t>
-        </is>
-      </c>
+          <t>(SA) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Terappia%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/OKESTREAM%20sao%20paulo</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Terappia aí em Sao paulo no Google e vi que vocês ainda não têm um site próprio para celular.
+Vi o perfil da OKESTREAM aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1990,17 +1994,17 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Terappia?</t>
+Posso te mandar a prévia demonstrativa que fiz para a OKESTREAM?</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>https://wa.me/5521999850091?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Terappia%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20OKESTREAM%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://wa.me/5521999850091?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Terappia%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20OKESTREAM%3F</t>
         </is>
       </c>
     </row>
@@ -2042,10 +2046,14 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(SA) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(11) 99153-0701</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5511991530701</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/Clnica%20de%20psicologia%20em%20So%20Paulo%20sao%20paulo</t>
@@ -2069,24 +2077,24 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clnica%20de%20psicologia%20em%20So%20Paulo%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5511991530701?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clnica%20de%20psicologia%20em%20So%20Paulo%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clnica%20de%20psicologia%20em%20So%20Paulo%3F</t>
+          <t>https://wa.me/5511991530701?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clnica%20de%20psicologia%20em%20So%20Paulo%3F</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Elton Alexandre, Psiclogo Vila Mariana So Pau</t>
+          <t>Pedro Pinto: Psiclogo em So Paulo e apoio LGB</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Elton Alexandre, Psicólogo Vila Mariana São Paulo - Telefone...</t>
+          <t>Pedro Pinto: Psicólogo em São Paulo e apoio LGBTQIA+</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2101,7 +2109,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Qual o telefone de Elton Alexandre, Psicólogo Vila Mariana São Paulo? O número de telefone é: +55 11...</t>
+          <t>Psicólogo em São Paulo e a Psicologia Clínica voltada à população LGBT. Telefone para ligação e What...</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2111,28 +2119,28 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.benditoguia.com.br/empresa/elton-alexandre-psicologo-vila-mariana-sao-paulo</t>
+          <t>https://emfoco.med.br/pedro-pinto-psicologo-em-sao-paulo-e-apoio-lgbtqia/</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(11) 95289-2329</t>
+          <t>(11) 3289-3195</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5511952892329</t>
+          <t>551132893195</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Elton%20Alexandre%2C%20Psiclogo%20Vila%20Mariana%20So%20Pau%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Pedro%20Pinto%3A%20Psiclogo%20em%20So%20Paulo%20e%20apoio%20LGB%20sao%20paulo</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Elton Alexandre, Psiclogo Vila Mariana So Pau aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Pedro Pinto: Psiclogo em So Paulo e apoio LGB aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2142,29 +2150,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Elton Alexandre, Psiclogo Vila Mariana So Pau?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Pedro Pinto: Psiclogo em So Paulo e apoio LGB?</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>https://wa.me/5511952892329?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Elton%20Alexandre%2C%20Psiclogo%20Vila%20Mariana%20So%20Pau%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/551132893195?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Pedro%20Pinto%3A%20Psiclogo%20em%20So%20Paulo%20e%20apoio%20LGB%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>https://wa.me/5511952892329?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Elton%20Alexandre%2C%20Psiclogo%20Vila%20Mariana%20So%20Pau%3F</t>
+          <t>https://wa.me/551132893195?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Pedro%20Pinto%3A%20Psiclogo%20em%20So%20Paulo%20e%20apoio%20LGB%3F</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Inddex PSICOLOGO GUSTAVO ROBERTO CNPJ...</t>
+          <t>Elton Alexandre, Psiclogo Vila Mariana So Pau</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Inddex · PSICOLOGO GUSTAVO ROBERTO · CNPJ...</t>
+          <t>Elton Alexandre, Psicólogo Vila Mariana São Paulo - Telefone...</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2179,7 +2187,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Inddex/SP/SAO Paulo/Psicologo Gustavo Roberto.Telefones, e-mail, capital social, sócios e CNAEs secu...</t>
+          <t>Qual o telefone de Elton Alexandre, Psicólogo Vila Mariana São Paulo? O número de telefone é: +55 11...</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2189,28 +2197,28 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://inddex.com.br/empresa/49186818000130/atividades-de-psicologia-e-psicanalise-sao-paulo-sp</t>
+          <t>https://www.benditoguia.com.br/empresa/elton-alexandre-psicologo-vila-mariana-sao-paulo</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(49) 1868-1800</t>
+          <t>(11) 95289-2329</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>554918681800</t>
+          <t>5511952892329</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Inddex%20PSICOLOGO%20GUSTAVO%20ROBERTO%20CNPJ...%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Elton%20Alexandre%2C%20Psiclogo%20Vila%20Mariana%20So%20Pau%20sao%20paulo</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Inddex PSICOLOGO GUSTAVO ROBERTO CNPJ... aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Elton Alexandre, Psiclogo Vila Mariana So Pau aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2220,29 +2228,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Inddex PSICOLOGO GUSTAVO ROBERTO CNPJ...?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Elton Alexandre, Psiclogo Vila Mariana So Pau?</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>https://wa.me/554918681800?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Inddex%20PSICOLOGO%20GUSTAVO%20ROBERTO%20CNPJ...%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5511952892329?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Elton%20Alexandre%2C%20Psiclogo%20Vila%20Mariana%20So%20Pau%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>https://wa.me/554918681800?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Inddex%20PSICOLOGO%20GUSTAVO%20ROBERTO%20CNPJ...%3F</t>
+          <t>https://wa.me/5511952892329?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Elton%20Alexandre%2C%20Psiclogo%20Vila%20Mariana%20So%20Pau%3F</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Psicloga Aline Quirosa, So Paulo (2026)</t>
+          <t>Bem Estar Psicologia</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Psicóloga Aline Quirosa, São Paulo (2026)</t>
+          <t>Bem Estar Psicologia | Psicólogos e Fonoaudiólogo em São ...</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2257,7 +2265,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brasil. São Paulo, SP. Psicóloga Aline Quirosa.Endereço. Telefone. Horário de Funcionamento. Notific...</t>
+          <t>Clínica de Psicologia e Fonoaudiologia na Zona Norte de São Paulo. Atendimento presencial e online p...</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2267,24 +2275,28 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.findhealthclinics.org/BR/São-Paulo/103266911851448/Psicóloga-Aline-Quirosa</t>
+          <t>https://www.bemestarpsicologia.com.br/</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(SA) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(11) 3867-8970</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>551138678970</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Psicloga%20Aline%20Quirosa%2C%20So%20Paulo%20%282026%29%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Bem%20Estar%20Psicologia%20sao%20paulo</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Psicloga Aline Quirosa, So Paulo (2026) aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Bem Estar Psicologia aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2294,29 +2306,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Psicloga Aline Quirosa, So Paulo (2026)?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Bem Estar Psicologia?</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psicloga%20Aline%20Quirosa%2C%20So%20Paulo%20%282026%29%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/551138678970?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Bem%20Estar%20Psicologia%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psicloga%20Aline%20Quirosa%2C%20So%20Paulo%20%282026%29%3F</t>
+          <t>https://wa.me/551138678970?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Bem%20Estar%20Psicologia%3F</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Clnica Psico Self</t>
+          <t>Clnica de Psiquiatria e Psicologia Vida Menta</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Clínica Psico Self – Psicologia e Bem Estar na Zona Norte ...</t>
+          <t>Clínica de Psiquiatria e Psicologia Vida Mental By CREMED</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2331,7 +2343,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>UNIDADE I - PSI Atendimento psicológico Parque Domingos Luís, 126 Jd. São Paulo UNIDADE II - PICS Te...</t>
+          <t>Psicologia Clínica Tratamentos de psicoterapia para a solução de problemas de saúde mental e promoçã...</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2341,24 +2353,28 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.clinicapsicoself.com.br/</t>
+          <t>https://vidamentalbycremed.com.br/</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(SA) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(11) 4114-0019</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>551141140019</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Clnica%20Psico%20Self%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Clnica%20de%20Psiquiatria%20e%20Psicologia%20Vida%20Menta%20sao%20paulo</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Clnica Psico Self aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Clnica de Psiquiatria e Psicologia Vida Menta aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2368,29 +2384,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Clnica Psico Self?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Clnica de Psiquiatria e Psicologia Vida Menta?</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clnica%20Psico%20Self%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/551141140019?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clnica%20de%20Psiquiatria%20e%20Psicologia%20Vida%20Menta%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clnica%20Psico%20Self%3F</t>
+          <t>https://wa.me/551141140019?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clnica%20de%20Psiquiatria%20e%20Psicologia%20Vida%20Menta%3F</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Bem Estar Psicologia</t>
+          <t>Link to facebook.com</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Bem Estar Psicologia | Psicólogos e Fonoaudiólogo em São ...</t>
+          <t>Link to facebook.com</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2405,38 +2421,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Clínica de Psicologia e Fonoaudiologia na Zona Norte de São Paulo. Atendimento presencial e online p...</t>
+          <t>The site owner hides the web page description....</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SITE ATIVO 📱</t>
+          <t>SEM SITE PRÓPRIO (OPORTUNIDADE 🔥)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.bemestarpsicologia.com.br/</t>
+          <t>Sem Site Cadastrado</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(11) 3867-8970</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>551138678970</t>
-        </is>
-      </c>
+          <t>(SA) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Bem%20Estar%20Psicologia%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Link%20to%20facebook.com%20sao%20paulo</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Bem Estar Psicologia aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Link to facebook.com aí em Sao paulo no Google e vi que vocês ainda não têm um site próprio para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2446,29 +2458,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Bem Estar Psicologia?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Link to facebook.com?</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://wa.me/551138678970?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Bem%20Estar%20Psicologia%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Link%20to%20facebook.com%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>https://wa.me/551138678970?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Bem%20Estar%20Psicologia%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Link%20to%20facebook.com%3F</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Incio</t>
+          <t>Elaine ferreira psicloga clnica, psicologo...</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Início - Instituto de Psiquiatria Paulista</t>
+          <t>Elaine ferreira psicóloga clínica, psicologo...</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2483,7 +2495,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Contamos com uma equipe de mais de 100 especialistas em psiquiatria, neurologia, neuropsicologia e p...</t>
+          <t>Bairro: Freguesia do Ó. Cidade: São Paulo. Estado: SP.Sua mensagem será enviada para nossa equipe e ...</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2493,28 +2505,28 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://psiquiatriapaulista.com.br/</t>
+          <t>https://www.terapyas.com.br/sobre/elaine-ferreira-psicologa-clinica-psicologo-atendimento-psicologico-e-terapia-sao-paulo-sp</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(22) 99977-0015</t>
+          <t>(11) 97622-2228</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>5522999770015</t>
+          <t>5511976222228</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Incio%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Elaine%20ferreira%20psicloga%20clnica%2C%20psicologo...%20sao%20paulo</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Incio aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Elaine ferreira psicloga clnica, psicologo... aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2524,29 +2536,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Incio?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Elaine ferreira psicloga clnica, psicologo...?</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://wa.me/5522999770015?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Incio%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5511976222228?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Elaine%20ferreira%20psicloga%20clnica%2C%20psicologo...%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>https://wa.me/5522999770015?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Incio%3F</t>
+          <t>https://wa.me/5511976222228?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Elaine%20ferreira%20psicloga%20clnica%2C%20psicologo...%3F</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Clnica de Psiquiatria e Psicologia Vida Menta</t>
+          <t>Ofertas e Cupons de</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Clínica de Psiquiatria e Psicologia Vida Mental By CREMED</t>
+          <t>Ofertas e Cupons de Desconto para Porto Alegre, Gramado e Mais!</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2561,7 +2573,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Psicologia Clínica Tratamentos de psicoterapia para a solução de problemas de saúde mental e promoçã...</t>
+          <t>Central de atendimento. Icone WhatsApp....</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2571,28 +2583,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://vidamentalbycremed.com.br/</t>
+          <t>https://www.tcheofertas.com.br/</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(11) 4114-0019</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>551141140019</t>
-        </is>
-      </c>
+          <t>(SA) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Clnica%20de%20Psiquiatria%20e%20Psicologia%20Vida%20Menta%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Ofertas%20e%20Cupons%20de%20sao%20paulo</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Clnica de Psiquiatria e Psicologia Vida Menta aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Ofertas e Cupons de aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2602,29 +2610,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Clnica de Psiquiatria e Psicologia Vida Menta?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Ofertas e Cupons de?</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>https://wa.me/551141140019?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clnica%20de%20Psiquiatria%20e%20Psicologia%20Vida%20Menta%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Ofertas%20e%20Cupons%20de%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>https://wa.me/551141140019?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clnica%20de%20Psiquiatria%20e%20Psicologia%20Vida%20Menta%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Ofertas%20e%20Cupons%20de%3F</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>JalaLive</t>
+          <t>Super Portal</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>JalaLive</t>
+          <t>Super Portal</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2639,7 +2647,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>LIVE Babak 2 Brazilian Serie D Esporte Clube São José Porto Alegre Esporte......</t>
+          <t>Marcação consulta/exame Atendimento....</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2649,7 +2657,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.jala7mjm.com/</t>
+          <t>https://portal-beneficiario.hapvida.com.br/</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2660,13 +2668,13 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/JalaLive%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Super%20Portal%20sao%20paulo</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da JalaLive aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Super Portal aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2676,29 +2684,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a JalaLive?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Super Portal?</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20JalaLive%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Super%20Portal%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20JalaLive%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Super%20Portal%3F</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Detran</t>
+          <t>PSI Site do CRP SP</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Detran</t>
+          <t>PSI Site do CRP SP</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2713,7 +2721,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Você não fez login, ou sua sessão expirou. Redirecionando para a página de login....</t>
+          <t>Para atendimento presencial, preferencialmente realize o agendamento prévio. Para demais consultas, ...</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2723,28 +2731,28 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.detran.sp.gov.br/session_timeout.do</t>
+          <t>https://www.crpsp.org/</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(11) 2178-9494</t>
+          <t>(11) 3065-9494</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>551121789494</t>
+          <t>551130659494</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Detran%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/PSI%20Site%20do%20CRP%20SP%20sao%20paulo</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Detran aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da PSI Site do CRP SP aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2754,29 +2762,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Detran?</t>
+Posso te mandar a prévia demonstrativa que fiz para a PSI Site do CRP SP?</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://wa.me/551121789494?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Detran%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/551130659494?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20PSI%20Site%20do%20CRP%20SP%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>https://wa.me/551121789494?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Detran%3F</t>
+          <t>https://wa.me/551130659494?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20PSI%20Site%20do%20CRP%20SP%3F</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Link to facebook.com</t>
+          <t>Fale Conosco</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Link to facebook.com</t>
+          <t>Fale Conosco</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2791,34 +2799,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>The site owner hides the web page description....</t>
+          <t>Para atendimento presencial, preferencialmente realize o agendamento prévio. Para demais consultas, ...</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SEM SITE PRÓPRIO (OPORTUNIDADE 🔥)</t>
+          <t>SITE ATIVO 📱</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sem Site Cadastrado</t>
+          <t>https://www.crpsp.org/contato</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(SA) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(11) 3080-1447</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>551130801447</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Link%20to%20facebook.com%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Fale%20Conosco%20sao%20paulo</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Link to facebook.com aí em Sao paulo no Google e vi que vocês ainda não têm um site próprio para celular.
+Vi o perfil da Fale Conosco aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2828,29 +2840,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Link to facebook.com?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Fale Conosco?</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Link%20to%20facebook.com%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/551130801447?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Fale%20Conosco%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Link%20to%20facebook.com%3F</t>
+          <t>https://wa.me/551130801447?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Fale%20Conosco%3F</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Elaine ferreira psicloga clnica, psicologo...</t>
+          <t>hering.com.br</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Elaine ferreira psicóloga clínica, psicologo...</t>
+          <t>hering.com.br</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2865,7 +2877,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bairro: Freguesia do Ó. Cidade: São Paulo. Estado: SP.Sua mensagem será enviada para nossa equipe e ...</t>
+          <t>Nossos canais oficias são: @Hering_oficial e @Ciaheringoficial no Instagram......</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2875,28 +2887,28 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.terapyas.com.br/sobre/elaine-ferreira-psicologa-clinica-psicologo-atendimento-psicologico-e-terapia-sao-paulo-sp</t>
+          <t>https://www.hering.com.br/</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(11) 97622-2228</t>
+          <t>(11) 3105-0422</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>5511976222228</t>
+          <t>551131050422</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Elaine%20ferreira%20psicloga%20clnica%2C%20psicologo...%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/hering.com.br%20sao%20paulo</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Elaine ferreira psicloga clnica, psicologo... aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da hering.com.br aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2906,29 +2918,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Elaine ferreira psicloga clnica, psicologo...?</t>
+Posso te mandar a prévia demonstrativa que fiz para a hering.com.br?</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://wa.me/5511976222228?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Elaine%20ferreira%20psicloga%20clnica%2C%20psicologo...%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/551131050422?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20hering.com.br%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>https://wa.me/5511976222228?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Elaine%20ferreira%20psicloga%20clnica%2C%20psicologo...%3F</t>
+          <t>https://wa.me/551131050422?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20hering.com.br%3F</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Pmela Dauzcuk Psiclogo, So Paulo</t>
+          <t>As 10 melhores barbearias de So Paulo</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Pâmela Dauzcuk Psicólogo, São Paulo - Agende uma consulta ...</t>
+          <t>As 10 melhores barbearias de São Paulo - O melhor de São Paulo</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2943,17 +2955,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Economize tempo agendando um horário online com Pâmela Dauzcuk, Psicólogo em São Paulo. Leia os come...</t>
+          <t>Selecionamos as melhores barbearias SP que se sobressaem pelo atendimento, qualidade dos serviços, s...</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SEM SITE (OPORTUNIDADE QUENTE 🔥)</t>
+          <t>SITE ATIVO 📱</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sem Site Cadastrado</t>
+          <t>https://www.melhoressaopaulo.com/barbearias/</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2964,13 +2976,13 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Pmela%20Dauzcuk%20Psiclogo%2C%20So%20Paulo%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/As%2010%20melhores%20barbearias%20de%20So%20Paulo%20sao%20paulo</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Pmela Dauzcuk Psiclogo, So Paulo aí em Sao paulo no Google e vi que vocês ainda não têm um site próprio para celular.
+Vi o perfil da As 10 melhores barbearias de So Paulo aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -2980,29 +2992,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Pmela Dauzcuk Psiclogo, So Paulo?</t>
+Posso te mandar a prévia demonstrativa que fiz para a As 10 melhores barbearias de So Paulo?</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Pmela%20Dauzcuk%20Psiclogo%2C%20So%20Paulo%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20As%2010%20melhores%20barbearias%20de%20So%20Paulo%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Pmela%20Dauzcuk%20Psiclogo%2C%20So%20Paulo%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20As%2010%20melhores%20barbearias%20de%20So%20Paulo%3F</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Terapia online com psiclogos disponveis 24h p</t>
+          <t>Barbearia em So Paulo</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Terapia online com psicólogos disponíveis 24h por dia | Zenklub</t>
+          <t>Barbearia em São Paulo - perto de mim - Cabeleireiro ...</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3017,7 +3029,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Estamos sempre com você. Todo dia e a qualquer hora, nossos especialistas estarão disponíveis para a...</t>
+          <t>Para evitar isso, use os mecanismos de localização do Booksy e encontre os lugares mais próximos da ...</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3027,24 +3039,28 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://zenklub.com.br/</t>
+          <t>https://booksy.com/pt-br/s/barbearias/1047773_sao-paulo</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(SA) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(11) 94990-8390</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>5511949908390</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Terapia%20online%20com%20psiclogos%20disponveis%2024h%20p%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Barbearia%20em%20So%20Paulo%20sao%20paulo</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Terapia online com psiclogos disponveis 24h p aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Barbearia em So Paulo aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3054,29 +3070,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Terapia online com psiclogos disponveis 24h p?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Barbearia em So Paulo?</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Terapia%20online%20com%20psiclogos%20disponveis%2024h%20p%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5511949908390?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Barbearia%20em%20So%20Paulo%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Terapia%20online%20com%20psiclogos%20disponveis%2024h%20p%3F</t>
+          <t>https://wa.me/5511949908390?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Barbearia%20em%20So%20Paulo%3F</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Ofertas e Cupons de</t>
+          <t>Os melhores barbeiros perto de mim em So Paul</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ofertas e Cupons de Desconto para Porto Alegre, Gramado e Mais!</t>
+          <t>Os melhores barbeiros perto de mim em São Paulo - Fresha</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3091,7 +3107,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Central de atendimento. Icone WhatsApp....</t>
+          <t>Agendar online com os melhores Barbeiros perto de você em São Paulo. Excelentes ofertas e descontos!...</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3101,7 +3117,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.tcheofertas.com.br/</t>
+          <t>https://www.fresha.com/lp/pt/bt/barbearias/br-são-paulo</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3112,13 +3128,13 @@
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Ofertas%20e%20Cupons%20de%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Os%20melhores%20barbeiros%20perto%20de%20mim%20em%20So%20Paul%20sao%20paulo</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Ofertas e Cupons de aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Os melhores barbeiros perto de mim em So Paul aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3128,29 +3144,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Ofertas e Cupons de?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Os melhores barbeiros perto de mim em So Paul?</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Ofertas%20e%20Cupons%20de%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Os%20melhores%20barbeiros%20perto%20de%20mim%20em%20So%20Paul%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Ofertas%20e%20Cupons%20de%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Os%20melhores%20barbeiros%20perto%20de%20mim%20em%20So%20Paul%3F</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Super Portal</t>
+          <t>Bar Recanto de Santa Barbara em So Paulo, SP.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Super Portal</t>
+          <t>Bar Recanto de Santa Barbara em São Paulo, SP...</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3165,7 +3181,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Marcação consulta/exame Atendimento....</t>
+          <t>O endereço de sua sede está localizada na Rua Callixto, 171 - Cidade Satelite Santa Barbara, Sao Pau...</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3175,24 +3191,28 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://portal-beneficiario.hapvida.com.br/</t>
+          <t>https://www.econodata.com.br/consulta-empresa/03523129000172-bar-e-restaurante-recanto-de-santa-barbara-ltda</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(SA) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(12) 3978-2200</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>551239782200</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Super%20Portal%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Bar%20Recanto%20de%20Santa%20Barbara%20em%20So%20Paulo%2C%20SP.%20sao%20paulo</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Super Portal aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Bar Recanto de Santa Barbara em So Paulo, SP. aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3202,29 +3222,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Super Portal?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Bar Recanto de Santa Barbara em So Paulo, SP.?</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Super%20Portal%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/551239782200?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Bar%20Recanto%20de%20Santa%20Barbara%20em%20So%20Paulo%2C%20SP.%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Super%20Portal%3F</t>
+          <t>https://wa.me/551239782200?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Bar%20Recanto%20de%20Santa%20Barbara%20em%20So%20Paulo%2C%20SP.%3F</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cotiza Vuelos, Paquetes, Hoteles y Autos</t>
+          <t>Brasil Rugby vs Barbarians</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cotiza Vuelos, Paquetes, Hoteles y Autos | LATAM en Chile</t>
+          <t>Brasil Rugby vs Barbarians - São Paulo SP - 20/11/2019... - YouTu</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3239,17 +3259,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Conoce tus derechos. Reorganización financiera / Capítulo 11. Intercambio de slots Sao Paulo (GRU)....</t>
+          <t>© 2026 Google LLC....</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SITE FORA DO AR / LINK QUEBRADO 🚨</t>
+          <t>SEM SITE PRÓPRIO (OPORTUNIDADE 🔥)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.latamairlines.com/</t>
+          <t>Sem Site Cadastrado</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3260,13 +3280,13 @@
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Cotiza%20Vuelos%2C%20Paquetes%2C%20Hoteles%20y%20Autos%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Brasil%20Rugby%20vs%20Barbarians%20sao%20paulo</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Cotiza Vuelos, Paquetes, Hoteles y Autos aí em Sao paulo no Google e fui tentar acessar o site de vocês e vi que está fora do ar.
+Vi o perfil da Brasil Rugby vs Barbarians aí em Sao paulo no Google e vi que vocês ainda não têm um site próprio para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3276,29 +3296,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Cotiza Vuelos, Paquetes, Hoteles y Autos?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Brasil Rugby vs Barbarians?</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Cotiza%20Vuelos%2C%20Paquetes%2C%20Hoteles%20y%20Autos%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20fui%20tentar%20acessar%20o%20site%20de%20voc%C3%AAs%20e%20vi%20que%20est%C3%A1%20fora%20do%20ar.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Brasil%20Rugby%20vs%20Barbarians%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Cotiza%20Vuelos%2C%20Paquetes%2C%20Hoteles%20y%20Autos%3F</t>
+          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Brasil%20Rugby%20vs%20Barbarians%3F</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PSI Site do CRP SP</t>
+          <t>JOSE LIMA FARIAS 02266642529</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PSI Site do CRP SP</t>
+          <t>JOSE LIMA FARIAS 02266642529 — CNPJ... | Sr. Watson</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3313,7 +3333,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Para atendimento presencial, preferencialmente realize o agendamento prévio. Para demais consultas, ...</t>
+          <t>Avenida sapopemba, 16255, cidade satelite santa barbara, sao paulo/SP, 08330-180. Abrir no Google Ma...</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3323,28 +3343,28 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.crpsp.org/</t>
+          <t>https://srwatson.io/empresa/jose-lima-farias-02266642529-34905124000138</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(11) 3065-9494</t>
+          <t>(02) 2666-4252</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>551130659494</t>
+          <t>550226664252</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/PSI%20Site%20do%20CRP%20SP%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/JOSE%20LIMA%20FARIAS%2002266642529%20sao%20paulo</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da PSI Site do CRP SP aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da JOSE LIMA FARIAS 02266642529 aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3354,29 +3374,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a PSI Site do CRP SP?</t>
+Posso te mandar a prévia demonstrativa que fiz para a JOSE LIMA FARIAS 02266642529?</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://wa.me/551130659494?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20PSI%20Site%20do%20CRP%20SP%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/550226664252?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20JOSE%20LIMA%20FARIAS%2002266642529%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>https://wa.me/551130659494?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20PSI%20Site%20do%20CRP%20SP%3F</t>
+          <t>https://wa.me/550226664252?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20JOSE%20LIMA%20FARIAS%2002266642529%3F</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Portal oficial do Governo da Bahia com servio</t>
+          <t>Mapas de muestra de Aguas de Santa Barbara ge</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Portal oficial do Governo da Bahia com serviços públicos online</t>
+          <t>Mapas de muestra de Aguas de Santa Barbara generados con la...</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3391,7 +3411,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Portal oficial do Governo da Bahia com serviços públicos online......</t>
+          <t>Muestras de recorte de mapas Aguas de Santa Barbara (Sao Paulo)-1....</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3401,24 +3421,28 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.ba.gov.br/</t>
+          <t>https://tools.paintmaps.com/es/recorte-de-mapa/BR/4-102061001/muestras</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(SA) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(11) 3388-8000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>551133888000</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Portal%20oficial%20do%20Governo%20da%20Bahia%20com%20servio%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Mapas%20de%20muestra%20de%20Aguas%20de%20Santa%20Barbara%20ge%20sao%20paulo</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Portal oficial do Governo da Bahia com servio aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Mapas de muestra de Aguas de Santa Barbara ge aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3428,29 +3452,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Portal oficial do Governo da Bahia com servio?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Mapas de muestra de Aguas de Santa Barbara ge?</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Portal%20oficial%20do%20Governo%20da%20Bahia%20com%20servio%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/551133888000?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Mapas%20de%20muestra%20de%20Aguas%20de%20Santa%20Barbara%20ge%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Portal%20oficial%20do%20Governo%20da%20Bahia%20com%20servio%3F</t>
+          <t>https://wa.me/551133888000?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Mapas%20de%20muestra%20de%20Aguas%20de%20Santa%20Barbara%20ge%3F</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Barbearia em So Paulo</t>
+          <t>FreeGuessr</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Barbearia em São Paulo - perto de mim - Cabeleireiro ...</t>
+          <t>FreeGuessr - Free GeoGuessr Alternative</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3465,7 +3489,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Para evitar isso, use os mecanismos de localização do Booksy e encontre os lugares mais próximos da ...</t>
+          <t>Free GeoGuessr game alternative with unlimited play. Play multiplayer GeoGuessr-like games with frie...</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3475,28 +3499,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://booksy.com/pt-br/s/barbearias/1047773_sao-paulo</t>
+          <t>https://freeguessr.com/</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(11) 94990-8390</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>5511949908390</t>
-        </is>
-      </c>
+          <t>(SA) 98877-6655</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Barbearia%20em%20So%20Paulo%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/FreeGuessr%20sao%20paulo</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Barbearia em So Paulo aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da FreeGuessr aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -3506,623 +3526,15 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Barbearia em So Paulo?</t>
+Posso te mandar a prévia demonstrativa que fiz para a FreeGuessr?</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>https://wa.me/5511949908390?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Barbearia%20em%20So%20Paulo%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20FreeGuessr%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
-        <is>
-          <t>https://wa.me/5511949908390?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Barbearia%20em%20So%20Paulo%3F</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>As 10 melhores barbearias de So Paulo</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>As 10 melhores barbearias de São Paulo - O melhor de São Paulo</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Sao paulo</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Centro / Região</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Selecionamos as melhores barbearias SP que se sobressaem pelo atendimento, qualidade dos serviços, s...</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>SITE ATIVO 📱</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.melhoressaopaulo.com/barbearias/</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(SA) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/As%2010%20melhores%20barbearias%20de%20So%20Paulo%20sao%20paulo</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da As 10 melhores barbearias de So Paulo aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
-Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
-Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
-A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
-Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a As 10 melhores barbearias de So Paulo?</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20As%2010%20melhores%20barbearias%20de%20So%20Paulo%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20As%2010%20melhores%20barbearias%20de%20So%20Paulo%3F</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Barbearia Hermanos</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Barbearia Hermanos - Barbearia em São Paulo, Barbeiro ...</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Sao paulo</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Centro / Região</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Na Barbearia Hermanos, acreditamos que o cuidado com a aparência vai muito além de um simples corte ...</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>SITE ATIVO 📱</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://barbeariahermanos.com.br/</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(11) 3333-5704</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>551133335704</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/Barbearia%20Hermanos%20sao%20paulo</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Barbearia Hermanos aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
-Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
-Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
-A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
-Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Barbearia Hermanos?</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>https://wa.me/551133335704?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Barbearia%20Hermanos%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>https://wa.me/551133335704?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Barbearia%20Hermanos%3F</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Barbearia Tarantino</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Barbearia Tarantino | www.barbeariatarantino.com.br | São Paulo</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Sao paulo</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Centro / Região</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Inaugurada em 2015, a Barbearia Tarantino tem uma pegada clássica sem perder a modernidade. Em 2016,...</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>SITE ATIVO 📱</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.barbeariatarantino.com.br/</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(11) 3384-5530</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>551133845530</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/Barbearia%20Tarantino%20sao%20paulo</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Barbearia Tarantino aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
-Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
-Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
-A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
-Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Barbearia Tarantino?</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>https://wa.me/551133845530?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Barbearia%20Tarantino%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>https://wa.me/551133845530?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Barbearia%20Tarantino%3F</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Bar Recanto de Santa Barbara em So Paulo, SP.</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Bar Recanto de Santa Barbara em São Paulo, SP...</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Sao paulo</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Centro / Região</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>O endereço de sua sede está localizada na Rua Callixto, 171 - Cidade Satelite Santa Barbara, Sao Pau...</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>SITE ATIVO 📱</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.econodata.com.br/consulta-empresa/03523129000172-bar-e-restaurante-recanto-de-santa-barbara-ltda</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(SA) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/Bar%20Recanto%20de%20Santa%20Barbara%20em%20So%20Paulo%2C%20SP.%20sao%20paulo</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Bar Recanto de Santa Barbara em So Paulo, SP. aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
-Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
-Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
-A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
-Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Bar Recanto de Santa Barbara em So Paulo, SP.?</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Bar%20Recanto%20de%20Santa%20Barbara%20em%20So%20Paulo%2C%20SP.%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Bar%20Recanto%20de%20Santa%20Barbara%20em%20So%20Paulo%2C%20SP.%3F</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Brasil Rugby vs Barbarians</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Brasil Rugby vs Barbarians - São Paulo SP - 20/11/2019... - YouTu</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Sao paulo</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Centro / Região</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>© 2026 Google LLC....</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>SEM SITE PRÓPRIO (OPORTUNIDADE 🔥)</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Sem Site Cadastrado</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>(11) 98104-2508</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>5511981042508</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/Brasil%20Rugby%20vs%20Barbarians%20sao%20paulo</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Brasil Rugby vs Barbarians aí em Sao paulo no Google e vi que vocês ainda não têm um site próprio para celular.
-Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
-Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
-A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
-Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Brasil Rugby vs Barbarians?</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>https://wa.me/5511981042508?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Brasil%20Rugby%20vs%20Barbarians%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>https://wa.me/5511981042508?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Brasil%20Rugby%20vs%20Barbarians%3F</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>JOSE LIMA FARIAS 02266642529</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>JOSE LIMA FARIAS 02266642529 — CNPJ... | Sr. Watson</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Sao paulo</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Centro / Região</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Avenida sapopemba, 16255, cidade satelite santa barbara, sao paulo/SP, 08330-180. Abrir no Google Ma...</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>SITE ATIVO 📱</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://srwatson.io/empresa/jose-lima-farias-02266642529-34905124000138</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(02) 2666-4252</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>550226664252</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/JOSE%20LIMA%20FARIAS%2002266642529%20sao%20paulo</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da JOSE LIMA FARIAS 02266642529 aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
-Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
-Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
-A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
-Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a JOSE LIMA FARIAS 02266642529?</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>https://wa.me/550226664252?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20JOSE%20LIMA%20FARIAS%2002266642529%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>https://wa.me/550226664252?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20JOSE%20LIMA%20FARIAS%2002266642529%3F</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Mapas de muestra de Aguas de Santa Barbara ge</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Mapas de muestra de Aguas de Santa Barbara generados con la...</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Sao paulo</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Centro / Região</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Muestras de recorte de mapas Aguas de Santa Barbara (Sao Paulo)-1....</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>SITE ATIVO 📱</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://tools.paintmaps.com/es/recorte-de-mapa/BR/4-102061001/muestras</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(SA) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/Mapas%20de%20muestra%20de%20Aguas%20de%20Santa%20Barbara%20ge%20sao%20paulo</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Mapas de muestra de Aguas de Santa Barbara ge aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
-Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
-Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
-A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
-Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Mapas de muestra de Aguas de Santa Barbara ge?</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Mapas%20de%20muestra%20de%20Aguas%20de%20Santa%20Barbara%20ge%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Mapas%20de%20muestra%20de%20Aguas%20de%20Santa%20Barbara%20ge%3F</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>FreeGuessr</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>FreeGuessr - Free GeoGuessr Alternative</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Sao paulo</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Centro / Região</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Free GeoGuessr game alternative with unlimited play. Play multiplayer GeoGuessr-like games with frie...</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>SITE ATIVO 📱</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://freeguessr.com/</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>(SA) 98877-6655</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/FreeGuessr%20sao%20paulo</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da FreeGuessr aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
-Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
-Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
-A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
-Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a FreeGuessr?</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>https://wa.me/5541988776655?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20FreeGuessr%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
         <is>
           <t>https://wa.me/5541988776655?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20FreeGuessr%3F</t>
         </is>

--- a/leads_psicologo_sao_paulo.xlsx
+++ b/leads_psicologo_sao_paulo.xlsx
@@ -491,7 +491,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LCS Psicologia</t>
+          <t>Lcs Psicologia</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -529,10 +529,8 @@
           <t>(11) 96862-0525</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5511968620525</t>
-        </is>
+      <c r="I2" t="n">
+        <v>5511968620525</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -569,7 +567,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CNPJ 46.506.509/0001-01</t>
+          <t>Cnpj 46.506.509/0001-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -755,10 +753,8 @@
           <t>(52) 8293-9100</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>555282939100</t>
-        </is>
+      <c r="I5" t="n">
+        <v>555282939100</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -795,7 +791,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Psicologo felipe faccioli</t>
+          <t>Psicologo Felipe Faccioli</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -833,10 +829,8 @@
           <t>(41) 9788-0145</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>554197880145</t>
-        </is>
+      <c r="I6" t="n">
+        <v>554197880145</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -873,7 +867,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Psiclogo, Conselheiro, Terapeuta perto de mim</t>
+          <t>Psiclogo, Conselheiro, Terapeuta Perto D</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -947,7 +941,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Consultrio de psiclogo em So Paulo</t>
+          <t>Consultrio de Psiclogo em So Paulo</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -985,10 +979,8 @@
           <t>(11) 97092-5229</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5511970925229</t>
-        </is>
+      <c r="I8" t="n">
+        <v>5511970925229</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1137,10 +1129,8 @@
           <t>(11) 99333-8208</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5511993338208</t>
-        </is>
+      <c r="I10" t="n">
+        <v>5511993338208</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1177,14 +1167,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Psicologo Transpessoal em Perdizes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>Psicologo Transpessoal Em Perdizes</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Psicologo Transpessoal Em Perdizes</t>
-        </is>
-      </c>
       <c r="C11" t="inlineStr">
         <is>
           <t>Sao paulo</t>
@@ -1215,10 +1205,8 @@
           <t>(11) 2368-1764</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>551123681764</t>
-        </is>
+      <c r="I11" t="n">
+        <v>551123681764</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1255,7 +1243,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Psiclogo, So Paulo, SP</t>
+          <t>Psiclogo, So Paulo</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1329,7 +1317,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>VLOG vivendo em Sao Paulo: brunch, brech &amp; bo</t>
+          <t>Vlog Vivendo em Sao Paulo: Brunch, Brech</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1403,7 +1391,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PSICLOGA ONLINE: Terapia por Videochamada /</t>
+          <t>Psicloga Online: Terapia por Videochamad</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1441,10 +1429,8 @@
           <t>(71) 99264-3441</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5571992643441</t>
-        </is>
+      <c r="I14" t="n">
+        <v>5571992643441</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1629,7 +1615,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ajuda emocional: quando aconselhvel procurar</t>
+          <t>Ajuda Emocional: Quando Aconselhvel Proc</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1741,10 +1727,8 @@
           <t>(21) 99985-0091</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5521999850091</t>
-        </is>
+      <c r="I18" t="n">
+        <v>5521999850091</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1819,10 +1803,8 @@
           <t>(02) 96777-3000</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>5502967773000</t>
-        </is>
+      <c r="I19" t="n">
+        <v>5502967773000</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1897,10 +1879,8 @@
           <t>(80) 0905-5555</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>558009055555</t>
-        </is>
+      <c r="I20" t="n">
+        <v>558009055555</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1937,7 +1917,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>OKESTREAM</t>
+          <t>Okestream</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2011,7 +1991,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Clnica de psicologia em So Paulo</t>
+          <t>Clnica de Psicologia em So Paulo</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2049,10 +2029,8 @@
           <t>(11) 99153-0701</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5511991530701</t>
-        </is>
+      <c r="I22" t="n">
+        <v>5511991530701</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -2089,7 +2067,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Pedro Pinto: Psiclogo em So Paulo e apoio LGB</t>
+          <t>Pedro Pinto: Psiclogo em So Paulo e Apoi</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2127,10 +2105,8 @@
           <t>(11) 3289-3195</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>551132893195</t>
-        </is>
+      <c r="I23" t="n">
+        <v>551132893195</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -2167,7 +2143,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Elton Alexandre, Psiclogo Vila Mariana So Pau</t>
+          <t>Elton Alexandre, Psiclogo Vila Mariana S</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2205,10 +2181,8 @@
           <t>(11) 95289-2329</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>5511952892329</t>
-        </is>
+      <c r="I24" t="n">
+        <v>5511952892329</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -2283,10 +2257,8 @@
           <t>(11) 3867-8970</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>551138678970</t>
-        </is>
+      <c r="I25" t="n">
+        <v>551138678970</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2323,7 +2295,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Clnica de Psiquiatria e Psicologia Vida Menta</t>
+          <t>Clnica de Psiquiatria e Psicologia Vida</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2361,10 +2333,8 @@
           <t>(11) 4114-0019</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>551141140019</t>
-        </is>
+      <c r="I26" t="n">
+        <v>551141140019</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2401,7 +2371,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Link to facebook.com</t>
+          <t>Link To Facebook.com</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2475,7 +2445,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Elaine ferreira psicloga clnica, psicologo...</t>
+          <t>Elaine Ferreira Psicloga Clnica, Psicolo</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2513,10 +2483,8 @@
           <t>(11) 97622-2228</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5511976222228</t>
-        </is>
+      <c r="I28" t="n">
+        <v>5511976222228</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2701,14 +2669,14 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>Psi Site do Crp</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>PSI Site do CRP SP</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>PSI Site do CRP SP</t>
-        </is>
-      </c>
       <c r="C31" t="inlineStr">
         <is>
           <t>Sao paulo</t>
@@ -2739,10 +2707,8 @@
           <t>(11) 3065-9494</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>551130659494</t>
-        </is>
+      <c r="I31" t="n">
+        <v>551130659494</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2817,10 +2783,8 @@
           <t>(11) 3080-1447</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>551130801447</t>
-        </is>
+      <c r="I32" t="n">
+        <v>551130801447</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2857,14 +2821,14 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>Hering.com.br</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>hering.com.br</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>hering.com.br</t>
-        </is>
-      </c>
       <c r="C33" t="inlineStr">
         <is>
           <t>Sao paulo</t>
@@ -2895,10 +2859,8 @@
           <t>(11) 3105-0422</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>551131050422</t>
-        </is>
+      <c r="I33" t="n">
+        <v>551131050422</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2935,7 +2897,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>As 10 melhores barbearias de So Paulo</t>
+          <t>As 10 Melhores Barbearias de So Paulo</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3047,10 +3009,8 @@
           <t>(11) 94990-8390</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>5511949908390</t>
-        </is>
+      <c r="I35" t="n">
+        <v>5511949908390</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -3087,7 +3047,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Os melhores barbeiros perto de mim em So Paul</t>
+          <t>Os Melhores Barbeiros Perto de Mim em So</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3161,7 +3121,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Bar Recanto de Santa Barbara em So Paulo, SP.</t>
+          <t>Bar Recanto de Santa Barbara em So Paulo</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3199,10 +3159,8 @@
           <t>(12) 3978-2200</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>551239782200</t>
-        </is>
+      <c r="I37" t="n">
+        <v>551239782200</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -3239,7 +3197,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Brasil Rugby vs Barbarians</t>
+          <t>Brasil Rugby Vs Barbarians</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3313,7 +3271,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>JOSE LIMA FARIAS 02266642529</t>
+          <t>Jose Lima Farias 02266642529</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3351,10 +3309,8 @@
           <t>(02) 2666-4252</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>550226664252</t>
-        </is>
+      <c r="I39" t="n">
+        <v>550226664252</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -3391,7 +3347,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Mapas de muestra de Aguas de Santa Barbara ge</t>
+          <t>Mapas de Muestra de Aguas de Santa Barba</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3429,10 +3385,8 @@
           <t>(11) 3388-8000</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>551133888000</t>
-        </is>
+      <c r="I40" t="n">
+        <v>551133888000</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -3469,7 +3423,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FreeGuessr</t>
+          <t>Freeguessr</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">

--- a/leads_psicologo_sao_paulo.xlsx
+++ b/leads_psicologo_sao_paulo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,12 +491,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Elaine Ferreira Psicloga Clnica, Psicolo</t>
+          <t>Psicologo Felipe Faccioli</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Elaine ferreira psicóloga clínica, psicologo...</t>
+          <t>Psicologo felipe faccioli - CNPJ 63.510.039/0001-79</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bairro: Freguesia do Ó. Cidade: São Paulo. Estado: SP.Dom: Fechado. Site elaine-ferreira-psicologa-c...</t>
+          <t>Consulte o CNPJ 63.510.039/0001-79 da empresa PSICOLOGO FELIPE FACCIOLI (FELIPE FACCIOLI DE SOUZA LT...</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -521,28 +521,28 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.terapyas.com.br/sobre/elaine-ferreira-psicologa-clinica-psicologo-atendimento-psicologico-e-terapia-sao-paulo-sp</t>
+          <t>https://cnpj.today/63510039000179</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(11) 97622-2228</t>
+          <t>(41) 97880-1450</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5511976222228</t>
+          <t>5541978801450</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Elaine%20Ferreira%20Psicloga%20Clnica%2C%20Psicolo%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Psicologo%20felipe%20faccioli%20sao%20paulo</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Elaine Ferreira Psicloga Clnica, Psicolo aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Psicologo felipe faccioli aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -552,29 +552,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Elaine Ferreira Psicloga Clnica, Psicolo?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Psicologo felipe faccioli?</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://wa.me/5511976222228?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Elaine%20Ferreira%20Psicloga%20Clnica%2C%20Psicolo%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5541978801450?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psicologo%20felipe%20faccioli%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://wa.me/5511976222228?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Elaine%20Ferreira%20Psicloga%20Clnica%2C%20Psicolo%3F</t>
+          <t>https://wa.me/5541978801450?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psicologo%20felipe%20faccioli%3F</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Equilibrio Psicologia Clinica</t>
+          <t>Psiclogo Clnico Particular em Perdizes</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Equilibrio Psicologia Clinica — psicologo em São Paulo/SP</t>
+          <t>Psicólogo Clínico Particular em Perdizes - OneLiv</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>A Equilibrio Psicologia Clinica oferece atendimento com psicólogo em São Paulo/SP, em um espaço acol...</t>
+          <t>"Precisa de ajuda? Explore uma lista completa de psicólogos em Perdizes e encontre o especialista pe...</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -599,28 +599,28 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://velora.tech/sp/sao-paulo/psicologo/equilibrio-psicologia-clinica-313048</t>
+          <t>https://oneliv.com.br/psicologo/sao-paulo/perdizes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(71) 94400-0105</t>
+          <t>(11) 97425-1474</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5571944000105</t>
+          <t>5511974251474</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Equilibrio%20Psicologia%20Clinica%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Psiclogo%20Clnico%20Particular%20em%20Perdizes%20sao%20paulo</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Equilibrio Psicologia Clinica aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Psiclogo Clnico Particular em Perdizes aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -630,29 +630,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Equilibrio Psicologia Clinica?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Psiclogo Clnico Particular em Perdizes?</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://wa.me/5571944000105?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Equilibrio%20Psicologia%20Clinica%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5511974251474?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psiclogo%20Clnico%20Particular%20em%20Perdizes%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://wa.me/5571944000105?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Equilibrio%20Psicologia%20Clinica%3F</t>
+          <t>https://wa.me/5511974251474?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psiclogo%20Clnico%20Particular%20em%20Perdizes%3F</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Clnica de Psiclogo</t>
+          <t>Terappia</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Clínica de Psicólogo - Agende Sua Sessão - São Paulo - Luana...</t>
+          <t>Terappia - Psicologia Online. Consultas a partir de R$ 40 ...</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -667,38 +667,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>De forma geral, a terapia online pode ser útil em praticamente todos os temas que um psicólogo clíni...</t>
+          <t>Terapia online com psicólogos via WhatsApp. Consultas a partir de R$ 40. Encontre o seu psicólogo on...</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SITE FORA DO AR (ERRO 404) 🚨</t>
+          <t>SEM SITE PRÓPRIO (OPORTUNIDADE 🔥)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://psicologaluanaamaral.com.br/psicologo/clinica-de-psicologo-agende-sua-sessao-sao-paulo/</t>
+          <t>Sem Site Cadastrado</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(11) 98215-4403</t>
+          <t>(21) 99985-0091</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5511982154403</t>
+          <t>5521999850091</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Clnica%20de%20Psiclogo%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Terappia%20sao%20paulo</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Clnica de Psiclogo aí em Sao paulo no Google e fui tentar acessar o site de vocês e vi que está fora do ar.
+Vi o perfil da Terappia aí em Sao paulo no Google e vi que vocês ainda não têm um site próprio para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -708,29 +708,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Clnica de Psiclogo?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Terappia?</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://wa.me/5511982154403?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clnica%20de%20Psiclogo%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20fui%20tentar%20acessar%20o%20site%20de%20voc%C3%AAs%20e%20vi%20que%20est%C3%A1%20fora%20do%20ar.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5521999850091?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Terappia%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://wa.me/5511982154403?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clnica%20de%20Psiclogo%3F</t>
+          <t>https://wa.me/5521999850091?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Terappia%3F</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Somente</t>
+          <t>Clnica de Psicologia em So Paulo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SOMENTE | SAUDE EMOCIONAL</t>
+          <t>Clínica de psicologia em São Paulo - PsicoClinic</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Descomplicamos o acesso à saúde emocional com um canal direto via WhatsApp, onde você pode agendar, ...</t>
+          <t>Com psicóloga em São Paulo referência em tratamentos de excelência, a PsicoClinic é reconhecida pelo...</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -755,28 +755,28 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.somente.com.br/</t>
+          <t>https://www.psicoclinic.com.br/</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(11) 93776-1645</t>
+          <t>(11) 91857-7779</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5511937761645</t>
+          <t>5511918577779</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Somente%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Clnica%20de%20psicologia%20em%20So%20Paulo%20sao%20paulo</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Somente aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Clnica de psicologia em So Paulo aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -786,29 +786,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Somente?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Clnica de psicologia em So Paulo?</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://wa.me/5511937761645?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Somente%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5511918577779?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Clnica%20de%20psicologia%20em%20So%20Paulo%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://wa.me/5511937761645?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Somente%3F</t>
+          <t>https://wa.me/5511918577779?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Clnica%20de%20psicologia%20em%20So%20Paulo%3F</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Psicloga Responde Perguntas Sobre Psicol</t>
+          <t>Bem Estar Psicologia</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Psicóloga responde perguntas sobre Psicologia e Psicoterapia</t>
+          <t>Bem Estar Psicologia | Psicólogos e Fonoaudiólogo em São ...</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cosulta com psicóloga online, neuropsicologo online, psicólogo online preço, psicologos em sao paulo...</t>
+          <t>Clínica de Psicologia e Fonoaudiologia na Zona Norte de São Paulo. Atendimento presencial e online p...</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -833,28 +833,28 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.psicologaresponde.com.br/2023/04/psicologa-responde-perguntas-sobre.html</t>
+          <t>https://www.bemestarpsicologia.com.br/</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(11) 99787-4512</t>
+          <t>(11) 94846-2683</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5511997874512</t>
+          <t>5511948462683</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Psicloga%20Responde%20Perguntas%20Sobre%20Psicol%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Bem%20Estar%20Psicologia%20sao%20paulo</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Psicloga Responde Perguntas Sobre Psicol aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Bem Estar Psicologia aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -864,29 +864,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Psicloga Responde Perguntas Sobre Psicol?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Bem Estar Psicologia?</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://wa.me/5511997874512?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psicloga%20Responde%20Perguntas%20Sobre%20Psicol%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5511948462683?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Bem%20Estar%20Psicologia%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://wa.me/5511997874512?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psicloga%20Responde%20Perguntas%20Sobre%20Psicol%3F</t>
+          <t>https://wa.me/5511948462683?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Bem%20Estar%20Psicologia%3F</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Psicloga Terapia de Casal</t>
+          <t>Elaine Ferreira Psicloga Clnica, Psicolo</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Psicóloga Terapia de Casal | terapia online | Ana Caroline Pina d</t>
+          <t>Elaine ferreira psicóloga clínica, psicologo...</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -901,38 +901,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>As consultas presenciais são apenas em São Paulo. Confira abaixo os consultórios com atendimentos pr...</t>
+          <t>Bairro: Freguesia do Ó. Cidade: São Paulo. Estado: SP.Sua mensagem será enviada para nossa equipe e ...</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SEM SITE (OPORTUNIDADE QUENTE 🔥)</t>
+          <t>SITE ATIVO 📱</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sem Site Cadastrado</t>
+          <t>https://www.terapyas.com.br/sobre/elaine-ferreira-psicologa-clinica-psicologo-atendimento-psicologico-e-terapia-sao-paulo-sp</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(11) 95091-1931</t>
+          <t>(11) 97622-2228</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5511950911931</t>
+          <t>5511976222228</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Psicloga%20Terapia%20de%20Casal%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Elaine%20ferreira%20psicloga%20clnica%2C%20psicologo...%20sao%20paulo</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Psicloga Terapia de Casal aí em Sao paulo no Google e vi que vocês ainda não têm um site próprio para celular.
+Vi o perfil da Elaine ferreira psicloga clnica, psicologo... aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -942,29 +942,29 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Psicloga Terapia de Casal?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Elaine ferreira psicloga clnica, psicologo...?</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://wa.me/5511950911931?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psicloga%20Terapia%20de%20Casal%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20voc%C3%AAs%20ainda%20n%C3%A3o%20t%C3%AAm%20um%20site%20pr%C3%B3prio%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5511976222228?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Elaine%20ferreira%20psicloga%20clnica%2C%20psicologo...%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://wa.me/5511950911931?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psicloga%20Terapia%20de%20Casal%3F</t>
+          <t>https://wa.me/5511976222228?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Elaine%20ferreira%20psicloga%20clnica%2C%20psicologo...%3F</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Nossos Contatos</t>
+          <t>Barbearia em So Paulo</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nossos contatos | Psicólogos São Paulo</t>
+          <t>Barbearia em São Paulo - perto de mim - Cabeleireiro ...</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Confira aqui todos os nossos contatos. Nosso nosso WhatsApp, e-mail, telefone, chat e endereço admin...</t>
+          <t>Para evitar isso, use os mecanismos de localização do Booksy e encontre os lugares mais próximos da ...</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -989,28 +989,28 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.psicologossaopaulo.com.br/contato/</t>
+          <t>https://booksy.com/pt-br/s/barbearias/1047773_sao-paulo</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(11) 98204-5631</t>
+          <t>(11) 94990-8390</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5511982045631</t>
+          <t>5511949908390</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Nossos%20Contatos%20sao%20paulo</t>
+          <t>https://www.google.com/maps/search/Barbearia%20em%20So%20Paulo%20sao%20paulo</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Nossos Contatos aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
+Vi o perfil da Barbearia em So Paulo aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
 Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
 Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
         </is>
@@ -1020,95 +1020,17 @@
           <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
 A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
 Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Nossos Contatos?</t>
+Posso te mandar a prévia demonstrativa que fiz para a Barbearia em So Paulo?</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://wa.me/5511982045631?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Nossos%20Contatos%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
+          <t>https://wa.me/5511949908390?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Barbearia%20em%20So%20Paulo%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://wa.me/5511982045631?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Nossos%20Contatos%3F</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Psicloga Sp Maristela Vallim Botari</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Psicóloga SP Maristela Vallim Botari | Terapia Humanizada na Av..</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Sao paulo</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Centro / Região</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Para agendar uma Consulta Acolhimento humanizado Whatsapp Psicóloga (11) 95091-1931. Terapia online ...</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SITE ATIVO 📱</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.psicologa-sp.com.br/</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(11) 95091-1931</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5511950911931</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/Psicloga%20Sp%20Maristela%20Vallim%20Botari%20sao%20paulo</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Olá, tudo bem? Meu nome é João, sou da agência Webfy. 🚀
-Vi o perfil da Psicloga Sp Maristela Vallim Botari aí em Sao paulo no Google e vi que o site de vocês está um pouco desatualizado para celular.
-Nós estamos selecionando 5 empresas na região para **GANHAR A CRIAÇÃO DE UM SITE NOVO 100% GRATUITO** para o nosso portfólio deste mês.
-Já deixei uma demonstração pronta. Posso te mandar o link para você dar uma olhada sem compromisso?</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Show! Como te falei, a **criação e o desenvolvimento do site saem 100% GRATUITOS** (você economiza cerca de R$ 2.000 que é o valor de mercado). 🎁
-A única coisa necessária é a taxa anual de hospedagem e servidor (R$ 599/ano ou parcelado), que é a taxa padrão que todo site na internet precisa ter para ficar online no seu nome com domínio próprio (.com.br).
-Incluso: Hospedagem rápida para celular, suporte, botão de WhatsApp e presença no Google!
-Posso te mandar a prévia demonstrativa que fiz para a Psicloga Sp Maristela Vallim Botari?</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://wa.me/5511950911931?text=Ol%C3%A1%2C%20tudo%20bem%3F%20Meu%20nome%20%C3%A9%20Jo%C3%A3o%2C%20sou%20da%20ag%C3%AAncia%20Webfy.%20%F0%9F%9A%80%0A%0AVi%20o%20perfil%20da%20Psicloga%20Sp%20Maristela%20Vallim%20Botari%20a%C3%AD%20em%20Sao%20paulo%20no%20Google%20e%20vi%20que%20o%20site%20de%20voc%C3%AAs%20est%C3%A1%20um%20pouco%20desatualizado%20para%20celular.%0A%0AN%C3%B3s%20estamos%20selecionando%205%20empresas%20na%20regi%C3%A3o%20para%20%2A%2AGANHAR%20A%20CRIA%C3%87%C3%83O%20DE%20UM%20SITE%20NOVO%20100%25%20GRATUITO%2A%2A%20para%20o%20nosso%20portf%C3%B3lio%20deste%20m%C3%AAs.%0A%0AJ%C3%A1%20deixei%20uma%20demonstra%C3%A7%C3%A3o%20pronta.%20Posso%20te%20mandar%20o%20link%20para%20voc%C3%AA%20dar%20uma%20olhada%20sem%20compromisso%3F</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>https://wa.me/5511950911931?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Psicloga%20Sp%20Maristela%20Vallim%20Botari%3F</t>
+          <t>https://wa.me/5511949908390?text=Show%21%20Como%20te%20falei%2C%20a%20%2A%2Acria%C3%A7%C3%A3o%20e%20o%20desenvolvimento%20do%20site%20saem%20100%25%20GRATUITOS%2A%2A%20%28voc%C3%AA%20economiza%20cerca%20de%20R%24%202.000%20que%20%C3%A9%20o%20valor%20de%20mercado%29.%20%F0%9F%8E%81%0A%0AA%20%C3%BAnica%20coisa%20necess%C3%A1ria%20%C3%A9%20a%20taxa%20anual%20de%20hospedagem%20e%20servidor%20%28R%24%20599/ano%20ou%20parcelado%29%2C%20que%20%C3%A9%20a%20taxa%20padr%C3%A3o%20que%20todo%20site%20na%20internet%20precisa%20ter%20para%20ficar%20online%20no%20seu%20nome%20com%20dom%C3%ADnio%20pr%C3%B3prio%20%28.com.br%29.%0A%0AIncluso%3A%20Hospedagem%20r%C3%A1pida%20para%20celular%2C%20suporte%2C%20bot%C3%A3o%20de%20WhatsApp%20e%20presen%C3%A7a%20no%20Google%21%0A%0APosso%20te%20mandar%20a%20pr%C3%A9via%20demonstrativa%20que%20fiz%20para%20a%20Barbearia%20em%20So%20Paulo%3F</t>
         </is>
       </c>
     </row>
